--- a/ORCAMENTOS - PROGRAMAS.xlsx
+++ b/ORCAMENTOS - PROGRAMAS.xlsx
@@ -13,12 +13,33 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={58a103f1-dd33-4feb-945b-33d07cb7211d}</author>
-    <author>tc={59b338c1-9e64-49b8-979f-68efb4bda97e}</author>
-    <author>tc={78ba7cb5-3b32-42cc-93fc-4c21d9a78262}</author>
+    <author>tc={0619dc93-171c-4da2-b441-412af1ac3113}</author>
+    <author>tc={2a7dcfa7-c60f-45b9-842b-040baa35e254}</author>
+    <author>tc={c04e08d9-b3a5-458c-a077-712e51e5ccf6}</author>
+    <author>tc={f06b32da-dd55-4e63-aef3-1f65e72a0c83}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{58a103f1-dd33-4feb-945b-33d07cb7211d}" ref="A73">
+    <comment authorId="0" xr:uid="{0619dc93-171c-4da2-b441-412af1ac3113}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@luisalnr@gmail.com manter apenas no Eixo VI - linha 163 da planilha
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{2a7dcfa7-c60f-45b9-842b-040baa35e254}" ref="E68">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Verificar esse valor, pelo QDD esse Projeto/Atividade só computa R$ 47.042.981,28 @luisalnr@gmail.com
+Reply:
+	De acordo com o SICAF, é este valor mesmo de R$ 97.285.647,31
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}" ref="A73">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -28,21 +49,14 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{59b338c1-9e64-49b8-979f-68efb4bda97e}" ref="A1">
+    <comment authorId="3" xr:uid="{f06b32da-dd55-4e63-aef3-1f65e72a0c83}" ref="E73">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	@luisalnr@gmail.com manter apenas no Eixo VI - linha 163 da planilha
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{78ba7cb5-3b32-42cc-93fc-4c21d9a78262}" ref="E68">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Verificar esse valor, pelo QDD esse Projeto/Atividade só computa R$ 47.042.981,28 @luisalnr@gmail.com
+	No QDD, consta valor inicial de R$2000, consideramos R$1000 ou R$2000 @rsena.acre@gmail.com
+Reply:
+	Apenas o valor relativo à obra = R$ 1.000,00
 </t>
       </text>
     </comment>
@@ -51,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="274">
   <si>
     <t>Eixo</t>
   </si>
@@ -83,7 +97,7 @@
     <t>18 – Gestão Ambiental</t>
   </si>
   <si>
-    <t>SEFAZ</t>
+    <t>715/199 - SEFAZ</t>
   </si>
   <si>
     <t>PROSPECÇÃO DE MERCADO DA ECONOMIA
@@ -93,7 +107,7 @@
     <t>Exclusivo</t>
   </si>
   <si>
-    <t>CDSA</t>
+    <t>715/512 - CDSA</t>
   </si>
   <si>
     <t>PROSPECÇÃO DE MERCADOS DA ECONOMIA
@@ -103,7 +117,7 @@
     <t>INCENTIVO E REGULAÇÃO DE SERVIÇOS AMBIENTAIS - CDSA.</t>
   </si>
   <si>
-    <t>SEMA</t>
+    <t>720/001 - SEMA</t>
   </si>
   <si>
     <t>PROMOÇÃO DO MEIO AMBIENTE E CIDADES SUSTENTÁVEIS E RESILIENTES.</t>
@@ -124,19 +138,19 @@
     <t>CONSOLIDAÇÃO DOS SISTEMAS DE OUVIDORIA.</t>
   </si>
   <si>
-    <t xml:space="preserve">SEMA (Fundo Est. de Meio Ambiente e Florestas) </t>
+    <t xml:space="preserve">720/622 - SEMA (Fundo Est. de Meio Ambiente e Florestas) </t>
   </si>
   <si>
     <t xml:space="preserve">20 – Agricultura </t>
   </si>
   <si>
-    <t>SEAGRI</t>
+    <t>753/001 - SEAGRI</t>
   </si>
   <si>
     <t>AMPLIAÇÃO DO PROGRAMA DE AQUISIÇÃO DE ALIMENTOS.</t>
   </si>
   <si>
-    <t>CAGEACRE</t>
+    <t>753/401 - CAGEACRE</t>
   </si>
   <si>
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DOS SERVIÇOS DA CAGEACRE.</t>
@@ -154,7 +168,7 @@
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DOS SERVIÇOS DA SEAGRI.</t>
   </si>
   <si>
-    <t>EMATER</t>
+    <t>753/402 - EMATER</t>
   </si>
   <si>
     <t>PROMOÇÃO DA ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL - ATER - EMATER.</t>
@@ -169,13 +183,13 @@
     <t>PROMOÇÃO DE FEIRAS E EVENTOS.</t>
   </si>
   <si>
-    <t>SEAGRI (Fundo Agropecuário (FUNAGRO))</t>
+    <t>753/610 - SEAGRI (Fundo Agropecuário - FUNAGRO)</t>
   </si>
   <si>
     <t>22 – Indústria</t>
   </si>
   <si>
-    <t>SEICT (Fundo de Desenvolvimento Sustentável (FDS))</t>
+    <t>761/615 - SEICT (Fundo de Desenvolvimento Sustentável - FDS)</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-FDS.</t>
@@ -184,7 +198,7 @@
     <t xml:space="preserve">23 – Comércio e Serviços </t>
   </si>
   <si>
-    <t>JUCEAC (SEFAZ)</t>
+    <t>715/205 - JUCEAC</t>
   </si>
   <si>
     <t>PROMOVER O PROCESSO DE LEGALIZAÇAO DE EMPRESAS, SIMPLIFICANDO, INTEGRANDO E DESBUROCRATIZANDO(SIMPLIFICA MAIS).</t>
@@ -193,7 +207,7 @@
     <t>Não Exclusivo</t>
   </si>
   <si>
-    <t>SEICT</t>
+    <t>761/001 - SEICT</t>
   </si>
   <si>
     <t>FOMENTAR O DESENVOLVIMENTO DA INDÚSTRIA E DO COMÉRCIO.</t>
@@ -202,7 +216,7 @@
     <t>FOMENTO AO DESENVOLVIMENTO DOS NEGÓCIOS NO ESTADO DO ACRE.</t>
   </si>
   <si>
-    <t>ANAC</t>
+    <t>761/506 - ANAC</t>
   </si>
   <si>
     <t>FOMENTO AO DESENVOLVIMENTO DOS NEGÓCIOS DO ESTADO DO ACRE.</t>
@@ -211,9 +225,6 @@
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-ANAC.</t>
   </si>
   <si>
-    <t>SEICT (Fundo de Desenv. Sustentável (FDS))</t>
-  </si>
-  <si>
     <t>FOMENTAR O DESENVOLVIMENTO DA INDÚSTRIA E DO COMÉRCIO DO ESTADO DO ACRE.</t>
   </si>
   <si>
@@ -223,7 +234,7 @@
     <t>04 – Administração</t>
   </si>
   <si>
-    <t>SEPLAN</t>
+    <t>713/001 - SEPLAN</t>
   </si>
   <si>
     <t>APRIMORAMENTO DA GESTÃO ORÇAMENTARIA.</t>
@@ -247,31 +258,34 @@
     <t>PROMOÇÃO DA TRANSIÇÃO E EFICIÊNCIA ENERGÉTICA NA ADMINISTRAÇÃO PÚBLICA.</t>
   </si>
   <si>
-    <t>SEAD</t>
+    <t>714/001 - SEAD</t>
+  </si>
+  <si>
+    <t>715/001 - SEFAZ</t>
   </si>
   <si>
     <t>06 - Segurança Pública</t>
   </si>
   <si>
-    <t>SEJUSP</t>
+    <t>719/001 - SEJUSP</t>
   </si>
   <si>
     <t>MONITORAMENTO AMBIENTAL-COMANDO E CONTROLE.</t>
   </si>
   <si>
-    <t>SEJUSP (Fundo Est. de Segurança (FUNDESEG))</t>
+    <t>719/637 - SEJUSP (Fundo Est. de Segurança - FUNDESEG)</t>
   </si>
   <si>
     <t>17 - Saneamento</t>
   </si>
   <si>
-    <t>SANEACRE</t>
+    <t>744/203 - SANEACRE</t>
   </si>
   <si>
     <t>EFICIÊNCIA ENERGÉTICA.</t>
   </si>
   <si>
-    <t>AGEAC</t>
+    <t>715/210 - AGEAC</t>
   </si>
   <si>
     <t>18 - Gestão Ambiental</t>
@@ -283,7 +297,7 @@
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-SEMA.</t>
   </si>
   <si>
-    <t>SEMA (Fundo Est. de Comando e Controle Ambiental)</t>
+    <t>720/605 - SEMA (Fundo Est. de Comando e Controle Ambiental)</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-IMAC.</t>
@@ -295,10 +309,10 @@
     <t>MANUTENÇÃO DA ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-FUNDO ESTADUAL DE MEIO AMBIENTE E FLORESTAS.</t>
   </si>
   <si>
-    <t>IMAC</t>
-  </si>
-  <si>
-    <t>IMC</t>
+    <t>720/202 - IMAC</t>
+  </si>
+  <si>
+    <t>720/215 - IMC</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-IMC.</t>
@@ -337,16 +351,13 @@
     <t>25 – Energia</t>
   </si>
   <si>
-    <t>AGEAC (SEOP)</t>
-  </si>
-  <si>
     <t>PROMOÇÃO DA REGULAÇÃO DE ENERGIA ELÉTRICA.</t>
   </si>
   <si>
     <t xml:space="preserve">26 – Transporte </t>
   </si>
   <si>
-    <t>DERACRE (SEHURB)</t>
+    <t>744/201 - DERACRE</t>
   </si>
   <si>
     <t>FORTALECIMENTO DAS AÇÕES DE APOIO AOS MUNICÍPIOS.</t>
@@ -364,22 +375,25 @@
     <t>03 - Essencial à Justiça</t>
   </si>
   <si>
-    <t>PGE</t>
+    <t>510/001 - PGE</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DA PGE.</t>
   </si>
   <si>
+    <t>715/199 - SEFAZ (Departamento do Tesouro Estadual)</t>
+  </si>
+  <si>
     <t>PROGRAMA ESTADUAL DE ENFRENTAMENTO ÀS DEMANDAS CONTINGENTES.</t>
   </si>
   <si>
-    <t>SEGOV</t>
+    <t>445/001 - SEGOV</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACONAIS-SEGOV.</t>
   </si>
   <si>
-    <t>SEPI</t>
+    <t>722/001 - SEPI</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E FINANCEIRAS-SEPI.</t>
@@ -400,16 +414,13 @@
     <t>ADMINISTRAÇÃO E GESTÃO DAS AGÊNCIAS E POSTOS FISCAIS.</t>
   </si>
   <si>
-    <t>SEFAZ (Depto. Tesouro Estadual)</t>
-  </si>
-  <si>
     <t xml:space="preserve">06 – Segurança Pública </t>
   </si>
   <si>
     <t>FORTALECIMENTO DAS AÇÕES DE ENFRENTAMENTO À VIOLÊNCIA CONTRA MULHER.</t>
   </si>
   <si>
-    <t xml:space="preserve">COORD. EST. PROTEÇÃO E DEFESA CIVIL </t>
+    <t>452/001 - DEFESA CIVIL</t>
   </si>
   <si>
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DOS SERVIÇOS DA DEFESA CIVIL-CEPDEC</t>
@@ -418,7 +429,7 @@
     <t>06 – Segurança Pública</t>
   </si>
   <si>
-    <t>CBMAC</t>
+    <t>609/001 - CBMAC</t>
   </si>
   <si>
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DOS SERVIÇOS DO CBMAC.</t>
@@ -427,16 +438,19 @@
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DO CBMAC.</t>
   </si>
   <si>
+    <t>609/632 - CBMAC (Fundo Esp. do Corpo de Bombeiros Militar do Estado do Acre - FUNESBOM)</t>
+  </si>
+  <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-FUNESBOM.</t>
   </si>
   <si>
-    <t>PCAC</t>
+    <t>451/001 - PCAC</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DAS UNIDADES DA PCAC.</t>
   </si>
   <si>
-    <t>IAPEN</t>
+    <t>719/209 - IAPEN</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DE PRÉDIOS DO SISTEMA PRISIONAL.</t>
@@ -445,7 +459,7 @@
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DA SEJUSP.</t>
   </si>
   <si>
-    <t>SEJUSP (Fundo Penitenciário)</t>
+    <t>719/626 - SEJUSP (Fundo Penitenciário do Estado do Acre)</t>
   </si>
   <si>
     <t>POLICIAMENTO COMUNITÁRIO INTEGRADO EM ÁREAS E PARQUES URBANOS.</t>
@@ -454,7 +468,7 @@
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DOS SERVIÇOS INTEGRADOS DE SEGURANÇA PÚBLICA</t>
   </si>
   <si>
-    <t>PMAC</t>
+    <t>608/001 - PMAC</t>
   </si>
   <si>
     <t>FORTALECIMENTO DA POLÍCIA MILITAR.</t>
@@ -469,7 +483,7 @@
     <t>08 - Assistência Social</t>
   </si>
   <si>
-    <t>SEASDH</t>
+    <t>760/001 - SEASDH</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-SEASDH.</t>
@@ -481,7 +495,7 @@
     <t>09 - Previdência Social</t>
   </si>
   <si>
-    <t>ACREPREVIDÊNCIA</t>
+    <t>714/211 - ACREPREVIDÊNCIA</t>
   </si>
   <si>
     <t>MANUTENÇÃO DA ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS DO ACREPREVIDÊNCIA.</t>
@@ -493,7 +507,7 @@
     <t xml:space="preserve">10 – Saúde </t>
   </si>
   <si>
-    <t>SESACRE (Fundo Estadual de Saúde (FUNDES))</t>
+    <t>721/607 - SESACRE (Fundo Estadual de Saúde - FUNDES)</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DA SESACRE.</t>
@@ -505,7 +519,7 @@
     <t>11 - Trabalho</t>
   </si>
   <si>
-    <t>SETE</t>
+    <t>759/001 - SETE</t>
   </si>
   <si>
     <t>PROMOÇÃO E DESENVOLVIMENTO DO TURISMO SUSTENTÁVEL EM SEUS DIVERSOS SEGMENTOS.</t>
@@ -517,7 +531,7 @@
     <t>12 - Educação</t>
   </si>
   <si>
-    <t>SEE</t>
+    <t>717/001 - SEE</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-SEE.</t>
@@ -529,7 +543,7 @@
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DA REDE ESTADUAL DE ENSINO.</t>
   </si>
   <si>
-    <t>IEPTEC</t>
+    <t>717/212 - IEPTEC</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-IEPTEC.</t>
@@ -544,13 +558,14 @@
     <t>13 - Cultura</t>
   </si>
   <si>
-    <t>FEM</t>
+    <t>717/303 - FEM</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DA FEM.</t>
   </si>
   <si>
-    <t>FEM (Funcultura)</t>
+    <t>717/628 - FEM (Fundo Estadual de Cultura 
+- Funcultura)</t>
   </si>
   <si>
     <t>FOMENTO A CULTURA: LEI ALDIR BLANC.</t>
@@ -562,19 +577,19 @@
     <t>14 - Diretos da Cidadania</t>
   </si>
   <si>
-    <t>ISE</t>
+    <t>719/213 - ISE</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DO ISE.</t>
   </si>
   <si>
-    <t>SEASDH (Fundo Est. Def. Consumidor (DEFC)</t>
+    <t>760/640 - SEASDH (Fundo Est. Def. Consumidor  - DEFC)</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS PÚBLICOS ESTADUAIS-FEDC.</t>
   </si>
   <si>
-    <t>SEMULHER</t>
+    <t>762/001 - SEMULHER</t>
   </si>
   <si>
     <t>FORTALECIMENTO DO ENFRENTAMENTO À VIOLÊNCIA CONTRA MULHERES.</t>
@@ -583,7 +598,7 @@
     <t xml:space="preserve">15 – Urbanismo </t>
   </si>
   <si>
-    <t>SEHURB</t>
+    <t>744/001 - SEHURB</t>
   </si>
   <si>
     <t>IMPLANTAÇÃO E URBANIZAÇÃO DE PARQUES.</t>
@@ -604,16 +619,13 @@
     <t>ESTUDOS, AVALIAÇÕES E ELABORAÇÕES DE PROJETOS.</t>
   </si>
   <si>
-    <t>DERACRE</t>
-  </si>
-  <si>
     <t>URBANIZAÇÃO DE ORLAS DO ACRE.</t>
   </si>
   <si>
-    <t>SEHURB (Fundo Est. Esp. Recup. Bacia Igarapé S. Francisco)</t>
-  </si>
-  <si>
-    <t>SEOP</t>
+    <t>744/643 - SEHURB (Fundo Est. Esp. Recup. Bacia Igarapé S. Francisco)</t>
+  </si>
+  <si>
+    <t>754/001 - SEOP</t>
   </si>
   <si>
     <t>MELHORIA E AMPLIAÇÃO DOS ESPAÇOS/EQUIPAMENTOS PÚBLICOS DE USO COLETIVO PARA A POPULAÇÃO ACREANA.</t>
@@ -637,13 +649,13 @@
     <t>16 – Habitação</t>
   </si>
   <si>
-    <t>SEHURB (Fundo Est. Habitação (FEH))</t>
+    <t>744/619 - SEHURB (Fundo Est. Habitação - FEH)</t>
   </si>
   <si>
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS-FEH.</t>
   </si>
   <si>
-    <t>COHAB (SEFAZ)</t>
+    <t xml:space="preserve">715/501 - COHAB </t>
   </si>
   <si>
     <t>AMPLIAÇÃO DO ACESSO À MORADIA DIGNA.</t>
@@ -661,18 +673,12 @@
     <t>SANEAMENTO INTEGRADO.</t>
   </si>
   <si>
-    <t>SANEACRE (SEOP)</t>
-  </si>
-  <si>
     <t>AMPLIAÇÃO E MELHORIA DOS SISTEMAS DE ABASTECIMENTO DE ÁGUA NOS MUNICÍPIOS DO ACRE.</t>
   </si>
   <si>
     <t>AMPLIAÇÃO E MELHORIA DOS SISTEMAS DE COLETA E TRATAMENTO DE ESGOTAMENTO SANITÁRIO NOS MUNICÍPIOS DO ACRE.</t>
   </si>
   <si>
-    <t>AGEACRE (SEOP)</t>
-  </si>
-  <si>
     <t>PROMOÇÃO DA REGULAÇÃO DO SANEAMENTO BÁSICO.</t>
   </si>
   <si>
@@ -682,7 +688,7 @@
     <t>19 - Ciência e Tecnologia</t>
   </si>
   <si>
-    <t>FUNTAC</t>
+    <t>761/301 - FUNTAC</t>
   </si>
   <si>
     <t>MELHORIA, MODERNIZAÇÃO E INOVAÇÃO DOS SERVIÇOS DA FUNTAC.</t>
@@ -691,7 +697,7 @@
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DA SEAGRI.</t>
   </si>
   <si>
-    <t>IDAF</t>
+    <t>753/207 - IDAF</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DO IDAF.</t>
@@ -736,7 +742,7 @@
     <t>27 - Desporto e Lazer</t>
   </si>
   <si>
-    <t>SEEL</t>
+    <t>718/001 - SEEL</t>
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO/SEEL.</t>
@@ -760,7 +766,7 @@
     <t>FORTALECIMENTO DAS AÇÕES DE PROTEÇÃO SOCIAL AOS POVOS INDÍGENAS.</t>
   </si>
   <si>
-    <t>SEASDH (Fundo de Assistência Social (FEAS))</t>
+    <t>760/608 - SEASDH (Fundo de Assistência Social - FEAS)</t>
   </si>
   <si>
     <t>CONCESSÃO DO BOLSA MORADIA TRANSITÓRIA.</t>
@@ -775,7 +781,7 @@
     <t>PROMOÇÃO DA POLÍTICA ESTADUAL DE CIDADANIA E DIREITOS HUMANOS.</t>
   </si>
   <si>
-    <t xml:space="preserve">PROCON (SEASDH) </t>
+    <t xml:space="preserve">719/216 - PROCON </t>
   </si>
   <si>
     <t>PROMOÇÃO DE AÇÕES DE FISCALIZAÇÃO-ROTA DA QUALIDADE.</t>
@@ -793,7 +799,7 @@
     <t>MANUTENÇÃO DAS ATIVIDADES ADMINISTRATIVAS E OPERACIONAIS DO INSTITUTO PROCON/AC.</t>
   </si>
   <si>
-    <t>SEADH (Fundo Estadual de Defesa do Consumidor (FEDC))</t>
+    <t>760/640 - SEADH (Fundo Estadual de Defesa do Consumidor - FEDC)</t>
   </si>
   <si>
     <t>CONSOLIDAÇÃO DAS POLÍTICAS PARA MULHERES.</t>
@@ -805,7 +811,7 @@
     <t>VALORIZAÇÃO DA CULTURA E DOS CONHECIMENTOS TRADICIONAIS INDÍGENAS.</t>
   </si>
   <si>
-    <t>ITERACRE (SEHURB)</t>
+    <t xml:space="preserve">744/206 - ITERACRE </t>
   </si>
   <si>
     <t>REGULARIZAÇÃO FUNDIÁRIA ESTADUAL RURAL.</t>
@@ -826,7 +832,7 @@
     <t xml:space="preserve">04 – Administração </t>
   </si>
   <si>
-    <t>CGE</t>
+    <t>448/001 - CGE</t>
   </si>
   <si>
     <t>IMPLEMENTAÇÃO DE POLÍTICAS DE TRANSPARÊNCIA PÚBLICA, OUVIDORIA, INTEGRIDADE E CONTROLE NA ADMINISTRAÇÃO PÚBLICA.</t>
@@ -838,13 +844,10 @@
     <t>Eixo VI – Educação Ambiental e Inovação Climática</t>
   </si>
   <si>
-    <t xml:space="preserve">SEMA (Fundo Estadual de Comando e Cont. Ambiental) </t>
-  </si>
-  <si>
     <t>19 – Ciência e Tecnologia</t>
   </si>
   <si>
-    <t>FAPAC</t>
+    <t>761/309 - FAPAC</t>
   </si>
   <si>
     <t>APOIO A GERAÇÃO E DIFUSÃO DE CONHECIMENTO POR MEIO DA PESQUISA CIENTÍFICA E TECNOLÓGICA.</t>
@@ -860,9 +863,6 @@
   </si>
   <si>
     <t xml:space="preserve">19 – Ciência e Tecnologia </t>
-  </si>
-  <si>
-    <t>SEICT (Fundo de Des. Sustentável (FDS))</t>
   </si>
   <si>
     <t>FORTALECIMENTO DO ECOSSISTEMA DE INOVAÇÃO.</t>
@@ -955,7 +955,7 @@
       <name val="Geist"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -966,12 +966,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1013,7 +1007,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1035,6 +1029,9 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1049,9 +1046,6 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1074,6 +1068,9 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -1102,47 +1099,41 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -1154,7 +1145,7 @@
     <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1268,22 +1259,22 @@
 
 <file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{8cc5fa4d-01aa-4145-84ff-48770e8cc73d}">
+  <Task id="{b50e36b7-5e74-4168-ae7d-4022b894adff}">
     <Anchor>
-      <Comment id="{58a103f1-dd33-4feb-945b-33d07cb7211d}"/>
+      <Comment id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}"/>
     </Anchor>
     <History>
-      <Event time="2026-06-05T13:55:13.00" id="{aa3f5a89-536e-4c22-805b-bcbf1b3befa9}">
+      <Event time="2026-06-05T13:55:13.00" id="{6aa7667b-d93b-4be4-b33e-5689492c863a}">
         <Attribution userId="placeholder@email.com" userName="Roseneide Sena" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{58a103f1-dd33-4feb-945b-33d07cb7211d}"/>
+          <Comment id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2026-06-05T13:55:13.00" id="{de3fd9ed-3abb-4ea2-b6ab-8588c4440e42}">
+      <Event time="2026-06-05T13:55:13.00" id="{d38ca453-1983-4476-98ee-5aff7b39107e}">
         <Attribution userId="placeholder@email.com" userName="Roseneide Sena" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{58a103f1-dd33-4feb-945b-33d07cb7211d}"/>
+          <Comment id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}"/>
         </Anchor>
         <Assign userId="luisalnr@gmail.com" userName="luisalnr@gmail.com" userProvider="google-sheets"/>
       </Event>
@@ -1298,8 +1289,11 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="luisalnr@gmail.com" id="{c8aa2788-73f2-4249-bc32-b1e33f3a5606}" userId="luisalnr@gmail.com" providerId="google-sheets"/>
-  <x18tc:person displayName="Roseneide Sena" id="{0e3de8c8-24a5-4dfe-8a24-563036686d17}" providerId="google-sheets"/>
+  <x18tc:person displayName="luisalnr@gmail.com" id="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" userId="luisalnr@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Roseneide Sena" id="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" providerId="google-sheets"/>
+  <x18tc:person displayName="Vinícius_Oikonomia" id="{96cb20ff-ca75-4803-bcce-b3200dd39887}" providerId="google-sheets"/>
+  <x18tc:person displayName="rsena.acre@gmail.com" id="{2b2a40fd-1d02-433a-97cf-450b5792e745}" userId="rsena.acre@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Luísa Ribeiro" id="{4a970b55-9de4-44b4-b664-773b73a5c0ca}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1361,7 +1355,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A168:G168" displayName="Tabela_4" name="Tabela_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A167:G167" displayName="Tabela_4" name="Tabela_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1381,7 +1375,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A193:H193" displayName="Tabela_5" name="Tabela_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A192:H192" displayName="Tabela_5" name="Tabela_5" id="5">
   <tableColumns count="8">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1402,7 +1396,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A198:H198" displayName="Tabela_6" name="Tabela_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A197:H197" displayName="Tabela_6" name="Tabela_6" id="6">
   <tableColumns count="8">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1423,7 +1417,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A211:H211" displayName="Tabela_7" name="Tabela_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A210:H210" displayName="Tabela_7" name="Tabela_7" id="7">
   <tableColumns count="8">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1639,23 +1633,35 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E68" dT="2026-06-03T21:29:16.00" personId="{0e3de8c8-24a5-4dfe-8a24-563036686d17}" id="{78ba7cb5-3b32-42cc-93fc-4c21d9a78262}" done="0">
+  <x18tc:threadedComment ref="E73" dT="2026-06-08T13:15:23.00" personId="{96cb20ff-ca75-4803-bcce-b3200dd39887}" id="{f06b32da-dd55-4e63-aef3-1f65e72a0c83}" done="0">
+    <x18tc:text xml:space="preserve">No QDD, consta valor inicial de R$2000, consideramos R$1000 ou R$2000 @rsena.acre@gmail.com</x18tc:text>
+    <x18tc:mentions>
+      <x18tc:mention mentionpersonId="{2b2a40fd-1d02-433a-97cf-450b5792e745}" mentionId="{c73ce117-07e8-445d-bb33-afc23e89eae7}" startIndex="70" length="21"/>
+    </x18tc:mentions>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="E73" dT="2026-06-08T13:38:54.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{521d4cde-75cd-454b-b98e-61333b99ef39}" parentId="{f06b32da-dd55-4e63-aef3-1f65e72a0c83}">
+    <x18tc:text xml:space="preserve">Apenas o valor relativo à obra = R$ 1.000,00</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="E68" dT="2026-06-03T21:29:16.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{2a7dcfa7-c60f-45b9-842b-040baa35e254}" done="1">
     <x18tc:text xml:space="preserve">Verificar esse valor, pelo QDD esse Projeto/Atividade só computa R$ 47.042.981,28 @luisalnr@gmail.com</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{c8aa2788-73f2-4249-bc32-b1e33f3a5606}" mentionId="{9df7a426-933c-4257-8802-2563a28038eb}" startIndex="82" length="19"/>
+      <x18tc:mention mentionpersonId="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" mentionId="{90f250da-d5e6-4196-b946-647c4ebac419}" startIndex="82" length="19"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A73" dT="2026-06-05T13:55:13.00" personId="{0e3de8c8-24a5-4dfe-8a24-563036686d17}" id="{58a103f1-dd33-4feb-945b-33d07cb7211d}" done="1">
+  <x18tc:threadedComment ref="E68" dT="2026-06-08T12:59:46.00" personId="{4a970b55-9de4-44b4-b664-773b73a5c0ca}" id="{17afef39-fefd-4e38-a3d5-af6658c0a1cb}" parentId="{2a7dcfa7-c60f-45b9-842b-040baa35e254}">
+    <x18tc:text xml:space="preserve">De acordo com o SICAF, é este valor mesmo de R$ 97.285.647,31</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A73" dT="2026-06-05T13:55:13.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}" done="1">
     <x18tc:text xml:space="preserve">Não apareceram os seguintes órgãos: TCE, TJAC, DPE, MPAC (estão listados na planilha anterior, mas não estão nesta) @luisalnr@gmail.com
 Assigned to luisalnr@gmail.com</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{c8aa2788-73f2-4249-bc32-b1e33f3a5606}" mentionId="{87e4c2e6-d876-49ae-b1b1-1fb58302fd68}" startIndex="116" length="19"/>
+      <x18tc:mention mentionpersonId="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" mentionId="{d1cca60a-a306-4c14-ba9a-197043d694a9}" startIndex="116" length="19"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-06-03T18:33:29.00" personId="{0e3de8c8-24a5-4dfe-8a24-563036686d17}" id="{59b338c1-9e64-49b8-979f-68efb4bda97e}" done="1">
+  <x18tc:threadedComment ref="A1" dT="2026-06-03T18:33:29.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{0619dc93-171c-4da2-b441-412af1ac3113}" done="1">
     <x18tc:text xml:space="preserve">@luisalnr@gmail.com manter apenas no Eixo VI - linha 163 da planilha</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{c8aa2788-73f2-4249-bc32-b1e33f3a5606}" mentionId="{f6a29011-bf93-4f8d-9a04-a9672bf85583}" startIndex="0" length="19"/>
+      <x18tc:mention mentionpersonId="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" mentionId="{942a7798-e932-4ddc-b0dd-143a787fd7f2}" startIndex="0" length="19"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1671,7 +1677,7 @@
     <col customWidth="1" min="1" max="1" width="19.75"/>
     <col customWidth="1" min="2" max="2" width="19.0"/>
     <col customWidth="1" min="3" max="3" width="15.75"/>
-    <col customWidth="1" min="4" max="4" width="23.13"/>
+    <col customWidth="1" min="4" max="4" width="42.13"/>
     <col customWidth="1" min="5" max="5" width="25.75"/>
     <col customWidth="1" min="6" max="6" width="28.5"/>
     <col customWidth="1" min="7" max="7" width="99.88"/>
@@ -1714,19 +1720,19 @@
       <c r="C2" s="6">
         <v>541.0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>5000000.0</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>2.229E7</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1740,19 +1746,19 @@
       <c r="C3" s="6">
         <v>541.0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>784910.8</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="9">
         <v>1.154E7</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1766,19 +1772,19 @@
       <c r="C4" s="6">
         <v>541.0</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>20000.0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="9">
         <v>1.155E7</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1792,19 +1798,19 @@
       <c r="C5" s="6">
         <v>541.0</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <v>247000.0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>1.12E7</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1818,19 +1824,19 @@
       <c r="C6" s="6">
         <v>541.0</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>53000.0</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>1.121E7</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1844,19 +1850,19 @@
       <c r="C7" s="6">
         <v>541.0</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>99000.0</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <v>1.123E7</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1870,19 +1876,19 @@
       <c r="C8" s="6">
         <v>541.0</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>3501000.0</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>1.124E7</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1896,19 +1902,19 @@
       <c r="C9" s="6">
         <v>541.0</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>112000.0</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>1.125E7</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1922,19 +1928,19 @@
       <c r="C10" s="6">
         <v>541.0</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>11000.0</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <v>1.126E7</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1948,19 +1954,19 @@
       <c r="C11" s="6">
         <v>541.0</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <v>1000.0</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="9">
         <v>1.124E7</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1974,10 +1980,10 @@
       <c r="C12" s="6">
         <v>605.0</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <v>6000000.0</v>
       </c>
       <c r="F12" s="14">
@@ -1986,7 +1992,7 @@
       <c r="G12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2000,19 +2006,19 @@
       <c r="C13" s="6">
         <v>605.0</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="15">
         <v>630809.49</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="9">
         <v>1.075E7</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2026,19 +2032,19 @@
       <c r="C14" s="6">
         <v>605.0</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="15">
         <v>590000.0</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <v>1.076E7</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2052,19 +2058,19 @@
       <c r="C15" s="6">
         <v>606.0</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="15">
         <v>1800000.0</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <v>1.077E7</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2078,19 +2084,19 @@
       <c r="C16" s="6">
         <v>606.0</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="15">
         <v>381000.0</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="9">
         <v>1.078E7</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2104,19 +2110,19 @@
       <c r="C17" s="6">
         <v>606.0</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="15">
         <v>1210000.0</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="9">
         <v>1.083E7</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2130,19 +2136,19 @@
       <c r="C18" s="6">
         <v>606.0</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="15">
         <v>2442771.45</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>2.15E7</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2156,19 +2162,19 @@
       <c r="C19" s="6">
         <v>608.0</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="15">
         <v>5.94462E7</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <v>1.079E7</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2182,19 +2188,19 @@
       <c r="C20" s="6">
         <v>608.0</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="15">
         <v>5000.0</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="9">
         <v>1.08E7</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2208,19 +2214,19 @@
       <c r="C21" s="6">
         <v>608.0</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="15">
         <v>3345000.0</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>1.081E7</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2234,19 +2240,19 @@
       <c r="C22" s="6">
         <v>608.0</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="15">
         <v>3.0008E7</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="9">
         <v>1.334E7</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2260,19 +2266,19 @@
       <c r="C23" s="6">
         <v>608.0</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="12">
         <v>2000000.0</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>1.079E7</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2286,19 +2292,19 @@
       <c r="C24" s="6">
         <v>122.0</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="12">
         <v>3890000.0</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>2.186E7</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2312,19 +2318,19 @@
       <c r="C25" s="6">
         <v>691.0</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="12">
         <v>1361000.0</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="9">
         <v>2.213E7</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2338,19 +2344,19 @@
       <c r="C26" s="6">
         <v>691.0</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E26" s="15">
         <v>805582.32</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <v>1.284E7</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2364,19 +2370,19 @@
       <c r="C27" s="6">
         <v>691.0</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E27" s="15">
         <v>509811.63</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="9">
         <v>1.285E7</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2390,19 +2396,19 @@
       <c r="C28" s="6">
         <v>691.0</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E28" s="15">
         <v>100000.0</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <v>1.353E7</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2416,19 +2422,19 @@
       <c r="C29" s="6">
         <v>691.0</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E29" s="15">
         <v>1285928.7</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="9">
         <v>2.184E7</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2442,19 +2448,19 @@
       <c r="C30" s="6">
         <v>691.0</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>52</v>
+      <c r="D30" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="E30" s="15">
         <v>710000.0</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="9">
         <v>1.344E7</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H30" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2468,19 +2474,19 @@
       <c r="C31" s="6">
         <v>691.0</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>52</v>
+      <c r="D31" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="E31" s="16">
         <v>380000.0</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="9">
         <v>1.345E7</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2515,215 +2521,215 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>54</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>55</v>
       </c>
       <c r="C34" s="20">
         <v>121.0</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="22">
+        <v>1058356.0</v>
+      </c>
+      <c r="F34" s="23">
+        <v>1.159E7</v>
+      </c>
+      <c r="G34" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="21">
-        <v>1058356.0</v>
-      </c>
-      <c r="F34" s="22">
-        <v>1.159E7</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="24" t="s">
+      <c r="H34" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="19" t="s">
         <v>54</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>55</v>
       </c>
       <c r="C35" s="20">
         <v>121.0</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" s="21">
+      <c r="D35" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="22">
         <v>2.60405782E7</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <v>1.162E7</v>
       </c>
-      <c r="G35" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H35" s="24" t="s">
+      <c r="G35" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H35" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="19" t="s">
         <v>54</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>55</v>
       </c>
       <c r="C36" s="20">
         <v>121.0</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="21">
+      <c r="D36" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="22">
         <v>1.60164502E8</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="23">
         <v>1.166E7</v>
       </c>
-      <c r="G36" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="H36" s="24" t="s">
+      <c r="G36" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="H36" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>54</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>55</v>
       </c>
       <c r="C37" s="20">
         <v>121.0</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="21">
+      <c r="D37" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="22">
         <v>5.0E7</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="23">
         <v>1.167E7</v>
       </c>
-      <c r="G37" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37" s="24" t="s">
+      <c r="G37" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38" s="20">
         <v>122.0</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="26">
+      <c r="D38" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="27">
         <v>7538452.78</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="23">
         <v>1.163E7</v>
       </c>
-      <c r="G38" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38" s="24" t="s">
+      <c r="G38" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" s="20">
         <v>752.0</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" s="27">
+      <c r="D39" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="23">
         <v>1.359E7</v>
       </c>
-      <c r="G39" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H39" s="28" t="s">
+      <c r="G39" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" s="20">
         <v>752.0</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="27">
+      <c r="D40" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="23">
         <v>1.358E7</v>
       </c>
-      <c r="G40" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H40" s="28" t="s">
+      <c r="G40" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="20">
         <v>752.0</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="27">
+      <c r="D41" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="23">
         <v>1.36E7</v>
       </c>
-      <c r="G41" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H41" s="28" t="s">
+      <c r="G41" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>65</v>
@@ -2731,25 +2737,25 @@
       <c r="C42" s="20">
         <v>542.0</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="28">
         <v>1198684.01</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="23">
         <v>1.347E7</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H42" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>65</v>
@@ -2757,25 +2763,25 @@
       <c r="C43" s="20">
         <v>542.0</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="23">
         <v>1.366E7</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H43" s="28" t="s">
+      <c r="H43" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>69</v>
@@ -2783,25 +2789,25 @@
       <c r="C44" s="20">
         <v>512.0</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="28">
         <v>31000.0</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="23">
         <v>1.133E7</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H44" s="28" t="s">
+      <c r="H44" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>69</v>
@@ -2809,25 +2815,25 @@
       <c r="C45" s="20">
         <v>752.0</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="23">
         <v>1.357E7</v>
       </c>
-      <c r="G45" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="28" t="s">
+      <c r="G45" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H45" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>73</v>
@@ -2835,25 +2841,25 @@
       <c r="C46" s="20">
         <v>122.0</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="22">
         <v>300000.0</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="23">
         <v>1.119E7</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="H46" s="28" t="s">
+      <c r="H46" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>73</v>
@@ -2861,25 +2867,25 @@
       <c r="C47" s="20">
         <v>122.0</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="22">
         <v>1832764.37</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="23">
         <v>2.163E7</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="H47" s="28" t="s">
+      <c r="H47" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>73</v>
@@ -2887,25 +2893,25 @@
       <c r="C48" s="20">
         <v>122.0</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="21">
+      <c r="E48" s="22">
         <v>1200.0</v>
       </c>
-      <c r="F48" s="22">
+      <c r="F48" s="23">
         <v>2.169E7</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="H48" s="28" t="s">
+      <c r="H48" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>73</v>
@@ -2913,25 +2919,25 @@
       <c r="C49" s="20">
         <v>122.0</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="22">
         <v>5000000.0</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="23">
         <v>2.17E7</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="G49" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="H49" s="28" t="s">
+      <c r="H49" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>73</v>
@@ -2939,25 +2945,25 @@
       <c r="C50" s="20">
         <v>122.0</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F50" s="23">
         <v>2.002E7</v>
       </c>
-      <c r="G50" s="22" t="s">
+      <c r="G50" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="H50" s="28" t="s">
+      <c r="H50" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>73</v>
@@ -2965,25 +2971,25 @@
       <c r="C51" s="20">
         <v>122.0</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="28">
         <v>1698810.85</v>
       </c>
-      <c r="F51" s="22">
+      <c r="F51" s="23">
         <v>2.169E7</v>
       </c>
-      <c r="G51" s="22" t="s">
+      <c r="G51" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="H51" s="28" t="s">
+      <c r="H51" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>73</v>
@@ -2991,25 +2997,25 @@
       <c r="C52" s="20">
         <v>122.0</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="28">
         <v>262000.0</v>
       </c>
-      <c r="F52" s="22">
+      <c r="F52" s="23">
         <v>2.171E7</v>
       </c>
-      <c r="G52" s="22" t="s">
+      <c r="G52" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="H52" s="28" t="s">
+      <c r="H52" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>73</v>
@@ -3017,25 +3023,25 @@
       <c r="C53" s="20">
         <v>541.0</v>
       </c>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="28">
         <v>8000.0</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F53" s="23">
         <v>1.14E7</v>
       </c>
-      <c r="G53" s="22" t="s">
+      <c r="G53" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H53" s="28" t="s">
+      <c r="H53" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>73</v>
@@ -3043,25 +3049,25 @@
       <c r="C54" s="20">
         <v>541.0</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F54" s="23">
         <v>1.142E7</v>
       </c>
-      <c r="G54" s="22" t="s">
+      <c r="G54" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H54" s="28" t="s">
+      <c r="H54" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>73</v>
@@ -3069,25 +3075,25 @@
       <c r="C55" s="20">
         <v>542.0</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="21">
+      <c r="E55" s="22">
         <v>3560000.0</v>
       </c>
-      <c r="F55" s="22">
+      <c r="F55" s="23">
         <v>1.127E7</v>
       </c>
-      <c r="G55" s="22" t="s">
+      <c r="G55" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="28" t="s">
+      <c r="H55" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>73</v>
@@ -3095,25 +3101,25 @@
       <c r="C56" s="20">
         <v>542.0</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="22">
         <v>546680.0</v>
       </c>
-      <c r="F56" s="22">
+      <c r="F56" s="23">
         <v>1.128E7</v>
       </c>
-      <c r="G56" s="22" t="s">
+      <c r="G56" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H56" s="28" t="s">
+      <c r="H56" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>73</v>
@@ -3121,25 +3127,25 @@
       <c r="C57" s="20">
         <v>542.0</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E57" s="21">
+      <c r="E57" s="22">
         <v>73000.0</v>
       </c>
-      <c r="F57" s="22">
+      <c r="F57" s="23">
         <v>2.164E7</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="H57" s="28" t="s">
+      <c r="H57" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>73</v>
@@ -3147,25 +3153,25 @@
       <c r="C58" s="20">
         <v>542.0</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E58" s="21">
+      <c r="E58" s="22">
         <v>6320710.0</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="26">
         <v>2.165E7</v>
       </c>
-      <c r="G58" s="22" t="s">
+      <c r="G58" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="H58" s="28" t="s">
+      <c r="H58" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>73</v>
@@ -3173,25 +3179,25 @@
       <c r="C59" s="20">
         <v>542.0</v>
       </c>
-      <c r="D59" s="20" t="s">
+      <c r="D59" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E59" s="21">
+      <c r="E59" s="22">
         <v>1000.0</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="23">
         <v>1.136E7</v>
       </c>
-      <c r="G59" s="22" t="s">
+      <c r="G59" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="H59" s="28" t="s">
+      <c r="H59" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>73</v>
@@ -3199,25 +3205,25 @@
       <c r="C60" s="20">
         <v>542.0</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D60" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="21">
+      <c r="E60" s="22">
         <v>4951904.0</v>
       </c>
-      <c r="F60" s="22">
+      <c r="F60" s="23">
         <v>1.137E7</v>
       </c>
-      <c r="G60" s="22" t="s">
+      <c r="G60" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="H60" s="28" t="s">
+      <c r="H60" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>73</v>
@@ -3225,25 +3231,25 @@
       <c r="C61" s="20">
         <v>542.0</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E61" s="21">
+      <c r="E61" s="22">
         <v>1000.0</v>
       </c>
-      <c r="F61" s="22">
+      <c r="F61" s="23">
         <v>1.139E7</v>
       </c>
-      <c r="G61" s="22" t="s">
+      <c r="G61" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="H61" s="28" t="s">
+      <c r="H61" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>73</v>
@@ -3251,25 +3257,25 @@
       <c r="C62" s="20">
         <v>542.0</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="21">
+      <c r="E62" s="22">
         <v>1000.0</v>
       </c>
-      <c r="F62" s="22">
+      <c r="F62" s="23">
         <v>1.135E7</v>
       </c>
-      <c r="G62" s="22" t="s">
+      <c r="G62" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="H62" s="28" t="s">
+      <c r="H62" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>73</v>
@@ -3277,25 +3283,25 @@
       <c r="C63" s="20">
         <v>542.0</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E63" s="21">
+      <c r="E63" s="22">
         <v>1000.0</v>
       </c>
-      <c r="F63" s="22">
+      <c r="F63" s="23">
         <v>1.137E7</v>
       </c>
-      <c r="G63" s="22" t="s">
+      <c r="G63" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="H63" s="28" t="s">
+      <c r="H63" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>73</v>
@@ -3303,25 +3309,25 @@
       <c r="C64" s="20">
         <v>542.0</v>
       </c>
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="21">
+      <c r="E64" s="22">
         <v>1000.0</v>
       </c>
-      <c r="F64" s="22">
+      <c r="F64" s="23">
         <v>1.139E7</v>
       </c>
-      <c r="G64" s="22" t="s">
+      <c r="G64" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="H64" s="28" t="s">
+      <c r="H64" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>73</v>
@@ -3329,25 +3335,25 @@
       <c r="C65" s="20">
         <v>542.0</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E65" s="27">
+      <c r="E65" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F65" s="22">
+      <c r="F65" s="23">
         <v>1.127E7</v>
       </c>
-      <c r="G65" s="22" t="s">
+      <c r="G65" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="H65" s="28" t="s">
+      <c r="H65" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>93</v>
@@ -3355,97 +3361,97 @@
       <c r="C66" s="20">
         <v>752.0</v>
       </c>
-      <c r="D66" s="20" t="s">
+      <c r="D66" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E66" s="28">
+        <v>70000.0</v>
+      </c>
+      <c r="F66" s="23">
+        <v>1.047E7</v>
+      </c>
+      <c r="G66" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="E66" s="27">
-        <v>70000.0</v>
-      </c>
-      <c r="F66" s="22">
-        <v>1.047E7</v>
-      </c>
-      <c r="G66" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="H66" s="24" t="s">
+      <c r="H66" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C67" s="20">
         <v>782.0</v>
       </c>
-      <c r="D67" s="20" t="s">
+      <c r="D67" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E67" s="30">
+        <v>4737384.18</v>
+      </c>
+      <c r="F67" s="23">
+        <v>1.17E7</v>
+      </c>
+      <c r="G67" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="E67" s="29">
-        <v>4737384.18</v>
-      </c>
-      <c r="F67" s="22">
-        <v>1.17E7</v>
-      </c>
-      <c r="G67" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="H67" s="24" t="s">
+      <c r="H67" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C68" s="20">
         <v>782.0</v>
       </c>
-      <c r="D68" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="29">
+      <c r="D68" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E68" s="30">
         <v>9.728564731E7</v>
       </c>
-      <c r="F68" s="22">
+      <c r="F68" s="23">
         <v>2.195E7</v>
       </c>
-      <c r="G68" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="H68" s="24" t="s">
+      <c r="G68" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H68" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" s="20">
         <v>782.0</v>
       </c>
-      <c r="D69" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E69" s="27">
+      <c r="D69" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E69" s="28">
         <v>480000.0</v>
       </c>
-      <c r="F69" s="22">
+      <c r="F69" s="23">
         <v>1.046E7</v>
       </c>
-      <c r="G69" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="H69" s="28" t="s">
+      <c r="G69" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H69" s="29" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3481,3147 +3487,3150 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="s">
+      <c r="A73" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B73" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B73" s="31" t="s">
+      <c r="C73" s="33">
+        <v>92.0</v>
+      </c>
+      <c r="D73" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="C73" s="32">
-        <v>92.0</v>
-      </c>
-      <c r="D73" s="33" t="s">
+      <c r="E73" s="35">
+        <v>1000.0</v>
+      </c>
+      <c r="F73" s="36">
+        <v>1.118E7</v>
+      </c>
+      <c r="G73" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="34">
-        <v>1000.0</v>
-      </c>
-      <c r="F73" s="35">
-        <v>1.118E7</v>
-      </c>
-      <c r="G73" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H73" s="28" t="s">
+      <c r="H73" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C74" s="20">
         <v>121.0</v>
       </c>
-      <c r="D74" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="27">
+      <c r="D74" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E74" s="28">
         <v>2.0E7</v>
       </c>
-      <c r="F74" s="22">
+      <c r="F74" s="23">
         <v>2.228E7</v>
       </c>
-      <c r="G74" s="22" t="s">
+      <c r="G74" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="H74" s="28" t="s">
+      <c r="H74" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C75" s="36">
+      <c r="A75" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C75" s="37">
         <v>122.0</v>
       </c>
-      <c r="D75" s="33" t="s">
+      <c r="D75" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E75" s="37">
+      <c r="E75" s="38">
         <v>100000.0</v>
       </c>
-      <c r="F75" s="35">
+      <c r="F75" s="36">
         <v>2.152E7</v>
       </c>
-      <c r="G75" s="35" t="s">
+      <c r="G75" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="H75" s="28" t="s">
+      <c r="H75" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C76" s="36">
+      <c r="A76" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C76" s="37">
         <v>122.0</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="D76" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="E76" s="34">
+      <c r="E76" s="35">
         <f>50000+60000</f>
         <v>110000</v>
       </c>
-      <c r="F76" s="35">
+      <c r="F76" s="36">
         <v>2.12E7</v>
       </c>
-      <c r="G76" s="35" t="s">
+      <c r="G76" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="H76" s="28" t="s">
+      <c r="H76" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B77" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C77" s="36">
+      <c r="A77" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77" s="37">
         <v>129.0</v>
       </c>
-      <c r="D77" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="37">
+      <c r="D77" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E77" s="38">
         <v>5456616.5</v>
       </c>
-      <c r="F77" s="35">
+      <c r="F77" s="36">
         <v>1.197E7</v>
       </c>
-      <c r="G77" s="35" t="s">
+      <c r="G77" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="H77" s="28" t="s">
+      <c r="H77" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C78" s="36">
+      <c r="A78" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="37">
         <v>129.0</v>
       </c>
-      <c r="D78" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="37">
+      <c r="D78" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E78" s="38">
         <v>6468075.0</v>
       </c>
-      <c r="F78" s="35">
+      <c r="F78" s="36">
         <v>1.199E7</v>
       </c>
-      <c r="G78" s="35" t="s">
+      <c r="G78" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="H78" s="28" t="s">
-        <v>45</v>
+      <c r="H78" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I78" s="39">
+        <v>4.0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C79" s="36">
+      <c r="A79" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C79" s="37">
         <v>129.0</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="37">
+      <c r="D79" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="38">
         <v>5020000.0</v>
       </c>
-      <c r="F79" s="35">
+      <c r="F79" s="36">
         <v>1.203E7</v>
       </c>
-      <c r="G79" s="35" t="s">
+      <c r="G79" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="H79" s="28" t="s">
+      <c r="H79" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B80" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C80" s="36">
+      <c r="A80" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" s="37">
         <v>129.0</v>
       </c>
-      <c r="D80" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="37">
+      <c r="D80" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="38">
         <v>5000000.0</v>
       </c>
-      <c r="F80" s="35">
+      <c r="F80" s="36">
         <v>1.204E7</v>
       </c>
-      <c r="G80" s="35" t="s">
+      <c r="G80" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="H80" s="28" t="s">
+      <c r="H80" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B81" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C81" s="36">
+      <c r="A81" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C81" s="37">
         <v>129.0</v>
       </c>
-      <c r="D81" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="37">
+      <c r="D81" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" s="38">
         <v>5250.0</v>
       </c>
-      <c r="F81" s="35">
+      <c r="F81" s="36">
         <v>2.221E7</v>
       </c>
-      <c r="G81" s="35" t="s">
+      <c r="G81" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="H81" s="28" t="s">
+      <c r="H81" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" s="36">
+      <c r="A82" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C82" s="37">
         <v>129.0</v>
       </c>
-      <c r="D82" s="38" t="s">
+      <c r="D82" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E82" s="38">
+        <v>1000000.0</v>
+      </c>
+      <c r="F82" s="36">
+        <v>1.197E7</v>
+      </c>
+      <c r="G82" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="H82" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" s="37">
+        <v>129.0</v>
+      </c>
+      <c r="D83" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E83" s="38">
+        <v>4000000.0</v>
+      </c>
+      <c r="F83" s="36">
+        <v>1.203E7</v>
+      </c>
+      <c r="G83" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="H83" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E82" s="37">
-        <v>1000000.0</v>
-      </c>
-      <c r="F82" s="35">
-        <v>1.197E7</v>
-      </c>
-      <c r="G82" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="H82" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B83" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C83" s="36">
-        <v>129.0</v>
-      </c>
-      <c r="D83" s="38" t="s">
+      <c r="C84" s="37">
+        <v>181.0</v>
+      </c>
+      <c r="D84" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E84" s="35">
+        <v>36000.0</v>
+      </c>
+      <c r="F84" s="36">
+        <v>1.365E7</v>
+      </c>
+      <c r="G84" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H84" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E83" s="37">
-        <v>4000000.0</v>
-      </c>
-      <c r="F83" s="35">
-        <v>1.203E7</v>
-      </c>
-      <c r="G83" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="H83" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B84" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C84" s="36">
-        <v>181.0</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="E84" s="34">
-        <v>36000.0</v>
-      </c>
-      <c r="F84" s="35">
-        <v>1.365E7</v>
-      </c>
-      <c r="G84" s="35" t="s">
+      <c r="C85" s="37">
+        <v>182.0</v>
+      </c>
+      <c r="D85" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="H84" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B85" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C85" s="36">
+      <c r="E85" s="35">
+        <v>1000.0</v>
+      </c>
+      <c r="F85" s="36">
+        <v>1.015E7</v>
+      </c>
+      <c r="G85" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="H85" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C86" s="37">
         <v>182.0</v>
       </c>
-      <c r="D85" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E85" s="34">
-        <v>1000.0</v>
-      </c>
-      <c r="F85" s="35">
-        <v>1.015E7</v>
-      </c>
-      <c r="G85" s="35" t="s">
+      <c r="D86" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E86" s="38">
+        <v>500000.0</v>
+      </c>
+      <c r="F86" s="36">
+        <v>1.012E7</v>
+      </c>
+      <c r="G86" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="H86" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="H85" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B86" s="31" t="s">
+      <c r="C87" s="37">
+        <v>182.0</v>
+      </c>
+      <c r="D87" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="C86" s="36">
-        <v>182.0</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E86" s="37">
-        <v>500000.0</v>
-      </c>
-      <c r="F86" s="35">
-        <v>1.012E7</v>
-      </c>
-      <c r="G86" s="35" t="s">
+      <c r="E87" s="38">
+        <v>1999000.0</v>
+      </c>
+      <c r="F87" s="36">
+        <v>1.014E7</v>
+      </c>
+      <c r="G87" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="H86" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B87" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C87" s="36">
-        <v>182.0</v>
-      </c>
-      <c r="D87" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E87" s="37">
-        <v>1999000.0</v>
-      </c>
-      <c r="F87" s="35">
-        <v>1.014E7</v>
-      </c>
-      <c r="G87" s="35" t="s">
+      <c r="H87" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" s="33">
+        <v>183.0</v>
+      </c>
+      <c r="D88" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="H87" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B88" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C88" s="32">
+      <c r="E88" s="38">
+        <v>200000.0</v>
+      </c>
+      <c r="F88" s="36">
+        <v>2.075E7</v>
+      </c>
+      <c r="G88" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="H88" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" s="37">
         <v>183.0</v>
       </c>
-      <c r="D88" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E88" s="37">
-        <v>200000.0</v>
-      </c>
-      <c r="F88" s="35">
-        <v>2.075E7</v>
-      </c>
-      <c r="G88" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="H88" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B89" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C89" s="36">
-        <v>183.0</v>
-      </c>
-      <c r="D89" s="33" t="s">
+      <c r="D89" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="E89" s="34">
+      <c r="E89" s="35">
         <v>3300000.0</v>
       </c>
-      <c r="F89" s="35">
+      <c r="F89" s="36">
         <v>1.105E7</v>
       </c>
-      <c r="G89" s="35" t="s">
+      <c r="G89" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="H89" s="28" t="s">
+      <c r="H89" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C90" s="20">
         <v>183.0</v>
       </c>
-      <c r="D90" s="20" t="s">
+      <c r="D90" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E90" s="27">
+      <c r="E90" s="28">
         <v>800.0</v>
       </c>
-      <c r="F90" s="22">
+      <c r="F90" s="23">
         <v>1.093E7</v>
       </c>
-      <c r="G90" s="22" t="s">
+      <c r="G90" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="H90" s="28" t="s">
+      <c r="H90" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B91" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C91" s="36">
+      <c r="A91" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B91" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C91" s="37">
         <v>183.0</v>
       </c>
-      <c r="D91" s="33" t="s">
+      <c r="D91" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="39">
+      <c r="E91" s="40">
         <f>600000+3700000</f>
         <v>4300000</v>
       </c>
-      <c r="F91" s="35">
+      <c r="F91" s="36">
         <v>1.116E7</v>
       </c>
-      <c r="G91" s="35" t="s">
+      <c r="G91" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="H91" s="28" t="s">
+      <c r="H91" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C92" s="20">
         <v>183.0</v>
       </c>
-      <c r="D92" s="20" t="s">
+      <c r="D92" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="E92" s="21">
+      <c r="E92" s="22">
         <v>1771713.29</v>
       </c>
-      <c r="F92" s="22">
+      <c r="F92" s="23">
         <v>1.093E7</v>
       </c>
-      <c r="G92" s="22" t="s">
+      <c r="G92" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="H92" s="28" t="s">
+      <c r="H92" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B93" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C93" s="36">
+      <c r="A93" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C93" s="37">
         <v>183.0</v>
       </c>
-      <c r="D93" s="33" t="s">
+      <c r="D93" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E93" s="39">
+      <c r="E93" s="40">
         <f>2800000</f>
         <v>2800000</v>
       </c>
-      <c r="F93" s="35">
+      <c r="F93" s="36">
         <v>1.116E7</v>
       </c>
-      <c r="G93" s="35" t="s">
+      <c r="G93" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="H93" s="28" t="s">
+      <c r="H93" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C94" s="36">
+      <c r="A94" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C94" s="37">
         <v>183.0</v>
       </c>
-      <c r="D94" s="33" t="s">
+      <c r="D94" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="40">
+      <c r="E94" s="41">
         <v>50000.0</v>
       </c>
-      <c r="F94" s="35">
+      <c r="F94" s="36">
         <v>1.115E7</v>
       </c>
-      <c r="G94" s="35" t="s">
+      <c r="G94" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="H94" s="28" t="s">
+      <c r="H94" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C95" s="32">
+      <c r="A95" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" s="33">
         <v>183.0</v>
       </c>
-      <c r="D95" s="33" t="s">
+      <c r="D95" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E95" s="40">
+      <c r="E95" s="41">
         <v>250000.0</v>
       </c>
-      <c r="F95" s="35">
+      <c r="F95" s="36">
         <v>1.112E7</v>
       </c>
-      <c r="G95" s="35" t="s">
+      <c r="G95" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="H95" s="28" t="s">
+      <c r="H95" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B96" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C96" s="32">
+      <c r="A96" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C96" s="33">
         <v>183.0</v>
       </c>
-      <c r="D96" s="33" t="s">
+      <c r="D96" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E96" s="40">
+      <c r="E96" s="41">
         <v>400000.0</v>
       </c>
-      <c r="F96" s="35">
+      <c r="F96" s="36">
         <v>1.115E7</v>
       </c>
-      <c r="G96" s="35" t="s">
+      <c r="G96" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="H96" s="28" t="s">
+      <c r="H96" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B97" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C97" s="36">
+      <c r="A97" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="37">
         <v>183.0</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="D97" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="E97" s="34">
+      <c r="E97" s="35">
         <f>3300000</f>
         <v>3300000</v>
       </c>
-      <c r="F97" s="35">
+      <c r="F97" s="36">
         <v>1.022E7</v>
       </c>
-      <c r="G97" s="35" t="s">
+      <c r="G97" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="H97" s="28" t="s">
+      <c r="H97" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B98" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="C98" s="36">
+      <c r="A98" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="37">
         <v>183.0</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D98" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="E98" s="40">
+      <c r="E98" s="41">
         <v>1000000.0</v>
       </c>
-      <c r="F98" s="35">
+      <c r="F98" s="36">
         <v>2.076E7</v>
       </c>
-      <c r="G98" s="35" t="s">
+      <c r="G98" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="H98" s="28" t="s">
+      <c r="H98" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B99" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C99" s="32">
-        <v>183.0</v>
-      </c>
-      <c r="D99" s="33" t="s">
+      <c r="A99" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C99" s="37">
+        <v>421.0</v>
+      </c>
+      <c r="D99" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="E99" s="40">
-        <v>800.0</v>
-      </c>
-      <c r="F99" s="35">
-        <v>1.093E7</v>
-      </c>
-      <c r="G99" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="H99" s="28" t="s">
+      <c r="E99" s="35">
+        <v>1000000.0</v>
+      </c>
+      <c r="F99" s="36">
+        <v>1.09E7</v>
+      </c>
+      <c r="G99" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="H99" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B100" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C100" s="36">
-        <v>421.0</v>
-      </c>
-      <c r="D100" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E100" s="34">
-        <v>1000000.0</v>
-      </c>
-      <c r="F100" s="35">
-        <v>1.09E7</v>
-      </c>
-      <c r="G100" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="H100" s="28" t="s">
-        <v>45</v>
+      <c r="A100" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C100" s="37">
+        <v>542.0</v>
+      </c>
+      <c r="D100" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E100" s="35">
+        <v>2779.13</v>
+      </c>
+      <c r="F100" s="36">
+        <v>1.347E7</v>
+      </c>
+      <c r="G100" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="H100" s="29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C101" s="36">
-        <v>542.0</v>
-      </c>
-      <c r="D101" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="E101" s="34">
-        <v>2779.13</v>
-      </c>
-      <c r="F101" s="35">
-        <v>1.347E7</v>
-      </c>
-      <c r="G101" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="H101" s="28" t="s">
-        <v>12</v>
+      <c r="A101" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C101" s="37">
+        <v>122.0</v>
+      </c>
+      <c r="D101" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="E101" s="35">
+        <v>1000.0</v>
+      </c>
+      <c r="F101" s="36">
+        <v>2.251E7</v>
+      </c>
+      <c r="G101" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="H101" s="29" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B102" s="31" t="s">
+      <c r="A102" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B102" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C102" s="36">
+      <c r="C102" s="20">
+        <v>244.0</v>
+      </c>
+      <c r="D102" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E102" s="28">
+        <v>5000000.0</v>
+      </c>
+      <c r="F102" s="23">
+        <v>1.221E7</v>
+      </c>
+      <c r="G102" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="H102" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B103" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" s="37">
         <v>122.0</v>
       </c>
-      <c r="D102" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="E102" s="34">
-        <v>1000.0</v>
-      </c>
-      <c r="F102" s="35">
-        <v>2.251E7</v>
-      </c>
-      <c r="G102" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="H102" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="C103" s="20">
-        <v>244.0</v>
-      </c>
-      <c r="D103" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E103" s="27">
-        <v>5000000.0</v>
-      </c>
-      <c r="F103" s="22">
-        <v>1.221E7</v>
-      </c>
-      <c r="G103" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="H103" s="28" t="s">
+      <c r="D103" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" s="41">
+        <v>100000.0</v>
+      </c>
+      <c r="F103" s="36">
+        <v>2.019E7</v>
+      </c>
+      <c r="G103" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="H103" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B104" s="31" t="s">
+      <c r="A104" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B104" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C104" s="36">
-        <v>122.0</v>
-      </c>
-      <c r="D104" s="38" t="s">
+      <c r="C104" s="20">
+        <v>272.0</v>
+      </c>
+      <c r="D104" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="E104" s="40">
-        <v>100000.0</v>
-      </c>
-      <c r="F104" s="35">
-        <v>2.019E7</v>
-      </c>
-      <c r="G104" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="H104" s="28" t="s">
+      <c r="E104" s="28">
+        <v>4000000.0</v>
+      </c>
+      <c r="F104" s="23">
+        <v>2.021E7</v>
+      </c>
+      <c r="G104" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="H104" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C105" s="20">
-        <v>272.0</v>
-      </c>
-      <c r="D105" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E105" s="27">
-        <v>4000000.0</v>
-      </c>
-      <c r="F105" s="22">
-        <v>2.021E7</v>
-      </c>
-      <c r="G105" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="H105" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B106" s="31" t="s">
+      <c r="A105" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B105" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C106" s="36">
+      <c r="C105" s="37">
         <v>302.0</v>
       </c>
-      <c r="D106" s="33" t="s">
+      <c r="D105" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="E106" s="39">
+      <c r="E105" s="40">
         <f>44510000</f>
         <v>44510000</v>
       </c>
-      <c r="F106" s="35">
+      <c r="F105" s="36">
         <v>1.173E7</v>
       </c>
-      <c r="G106" s="35" t="s">
+      <c r="G105" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="H106" s="28" t="s">
+      <c r="H105" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C106" s="37">
+        <v>302.0</v>
+      </c>
+      <c r="D106" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E106" s="38">
+        <v>1.2997E7</v>
+      </c>
+      <c r="F106" s="36">
+        <v>2.208E7</v>
+      </c>
+      <c r="G106" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="H106" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B107" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C107" s="36">
-        <v>302.0</v>
-      </c>
-      <c r="D107" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E107" s="37">
-        <v>1.2997E7</v>
-      </c>
-      <c r="F107" s="35">
-        <v>2.208E7</v>
-      </c>
-      <c r="G107" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="H107" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B108" s="31" t="s">
+      <c r="A107" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B107" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C108" s="36">
+      <c r="C107" s="37">
         <v>695.0</v>
       </c>
-      <c r="D108" s="33" t="s">
+      <c r="D107" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="E108" s="39">
+      <c r="E107" s="40">
         <f>700000+1</f>
         <v>700001</v>
       </c>
-      <c r="F108" s="35">
+      <c r="F107" s="36">
         <v>1.151E7</v>
       </c>
-      <c r="G108" s="35" t="s">
+      <c r="G107" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="H108" s="28" t="s">
-        <v>45</v>
+      <c r="H107" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C108" s="37">
+        <v>695.0</v>
+      </c>
+      <c r="D108" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="E108" s="38">
+        <v>1.0</v>
+      </c>
+      <c r="F108" s="36">
+        <v>1152000.0</v>
+      </c>
+      <c r="G108" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="H108" s="29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B109" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C109" s="36">
-        <v>695.0</v>
-      </c>
-      <c r="D109" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E109" s="37">
-        <v>1.0</v>
-      </c>
-      <c r="F109" s="35">
-        <v>1152000.0</v>
-      </c>
-      <c r="G109" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="H109" s="28" t="s">
-        <v>12</v>
+      <c r="A109" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B109" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C109" s="37">
+        <v>361.0</v>
+      </c>
+      <c r="D109" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="E109" s="38">
+        <v>1900000.0</v>
+      </c>
+      <c r="F109" s="36">
+        <v>2.089E7</v>
+      </c>
+      <c r="G109" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="H109" s="29" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B110" s="31" t="s">
+      <c r="A110" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B110" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C110" s="36">
+      <c r="C110" s="37">
         <v>361.0</v>
       </c>
-      <c r="D110" s="33" t="s">
+      <c r="D110" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="E110" s="37">
-        <v>1900000.0</v>
-      </c>
-      <c r="F110" s="35">
-        <v>2.089E7</v>
-      </c>
-      <c r="G110" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="H110" s="28" t="s">
+      <c r="E110" s="38">
+        <v>2.495E7</v>
+      </c>
+      <c r="F110" s="36">
+        <v>1.041E7</v>
+      </c>
+      <c r="G110" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="H110" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B111" s="31" t="s">
+      <c r="A111" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B111" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C111" s="36">
-        <v>361.0</v>
-      </c>
-      <c r="D111" s="33" t="s">
+      <c r="C111" s="37">
+        <v>362.0</v>
+      </c>
+      <c r="D111" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="E111" s="37">
-        <v>2.495E7</v>
-      </c>
-      <c r="F111" s="35">
-        <v>1.041E7</v>
-      </c>
-      <c r="G111" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="H111" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B112" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C112" s="36">
-        <v>362.0</v>
-      </c>
-      <c r="D112" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E112" s="34">
+      <c r="E111" s="35">
         <f>4000000</f>
         <v>4000000</v>
       </c>
-      <c r="F112" s="35">
+      <c r="F111" s="36">
         <v>1.04E7</v>
       </c>
-      <c r="G112" s="35" t="s">
+      <c r="G111" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="H112" s="28" t="s">
+      <c r="H111" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B112" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" s="37">
+        <v>363.0</v>
+      </c>
+      <c r="D112" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E112" s="38">
+        <v>500.0</v>
+      </c>
+      <c r="F112" s="36">
+        <v>2.082E7</v>
+      </c>
+      <c r="G112" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="H112" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B113" s="31" t="s">
+      <c r="A113" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B113" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C113" s="36">
+      <c r="C113" s="37">
         <v>363.0</v>
       </c>
-      <c r="D113" s="33" t="s">
+      <c r="D113" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="E113" s="37">
+      <c r="E113" s="38">
         <v>500.0</v>
       </c>
-      <c r="F113" s="35">
-        <v>2.082E7</v>
-      </c>
-      <c r="G113" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="H113" s="28" t="s">
+      <c r="F113" s="36">
+        <v>1.025E7</v>
+      </c>
+      <c r="G113" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="H113" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B114" s="31" t="s">
+      <c r="A114" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B114" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C114" s="36">
+      <c r="C114" s="37">
         <v>363.0</v>
       </c>
-      <c r="D114" s="33" t="s">
+      <c r="D114" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="E114" s="37">
-        <v>500.0</v>
-      </c>
-      <c r="F114" s="35">
-        <v>1.025E7</v>
-      </c>
-      <c r="G114" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="H114" s="28" t="s">
+      <c r="E114" s="38">
+        <v>1601000.0</v>
+      </c>
+      <c r="F114" s="36">
+        <v>1.023E7</v>
+      </c>
+      <c r="G114" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H114" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B115" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C115" s="36">
-        <v>363.0</v>
-      </c>
-      <c r="D115" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="E115" s="37">
-        <v>1601000.0</v>
-      </c>
-      <c r="F115" s="35">
-        <v>1.023E7</v>
-      </c>
-      <c r="G115" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="H115" s="28" t="s">
+      <c r="A115" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B115" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C115" s="37">
+        <v>122.0</v>
+      </c>
+      <c r="D115" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="E115" s="38">
+        <v>147472.27</v>
+      </c>
+      <c r="F115" s="36">
+        <v>1.299E7</v>
+      </c>
+      <c r="G115" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="H115" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B116" s="31" t="s">
+      <c r="A116" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B116" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C116" s="36">
+      <c r="C116" s="37">
         <v>122.0</v>
       </c>
-      <c r="D116" s="43" t="s">
+      <c r="D116" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="E116" s="38">
+        <v>151000.0</v>
+      </c>
+      <c r="F116" s="36">
+        <v>1.299E7</v>
+      </c>
+      <c r="G116" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="H116" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B117" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C117" s="33">
+        <v>392.0</v>
+      </c>
+      <c r="D117" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="E116" s="37">
-        <v>147472.27</v>
-      </c>
-      <c r="F116" s="35">
-        <v>1.299E7</v>
-      </c>
-      <c r="G116" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="H116" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B117" s="31" t="s">
+      <c r="E117" s="38">
+        <v>750000.0</v>
+      </c>
+      <c r="F117" s="36">
+        <v>1.29E7</v>
+      </c>
+      <c r="G117" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H117" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B118" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C117" s="36">
-        <v>122.0</v>
-      </c>
-      <c r="D117" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E117" s="37">
-        <v>151000.0</v>
-      </c>
-      <c r="F117" s="35">
-        <v>1.299E7</v>
-      </c>
-      <c r="G117" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="H117" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B118" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="C118" s="32">
+      <c r="C118" s="33">
         <v>392.0</v>
       </c>
-      <c r="D118" s="38" t="s">
+      <c r="D118" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="E118" s="37">
-        <v>750000.0</v>
-      </c>
-      <c r="F118" s="35">
-        <v>1.29E7</v>
-      </c>
-      <c r="G118" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="H118" s="28" t="s">
+      <c r="E118" s="38">
+        <v>290000.0</v>
+      </c>
+      <c r="F118" s="36">
+        <v>1.292E7</v>
+      </c>
+      <c r="G118" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="H118" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B119" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="C119" s="32">
-        <v>392.0</v>
-      </c>
-      <c r="D119" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E119" s="37">
-        <v>290000.0</v>
-      </c>
-      <c r="F119" s="35">
-        <v>1.292E7</v>
-      </c>
-      <c r="G119" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="H119" s="28" t="s">
+      <c r="A119" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B119" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C119" s="37">
+        <v>243.0</v>
+      </c>
+      <c r="D119" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E119" s="35">
+        <v>2251384.93</v>
+      </c>
+      <c r="F119" s="36">
+        <v>1.011E7</v>
+      </c>
+      <c r="G119" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="H119" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B120" s="31" t="s">
+      <c r="A120" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B120" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C120" s="36">
-        <v>243.0</v>
-      </c>
-      <c r="D120" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="E120" s="34">
-        <v>2251384.93</v>
-      </c>
-      <c r="F120" s="35">
-        <v>1.011E7</v>
-      </c>
-      <c r="G120" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="H120" s="28" t="s">
+      <c r="C120" s="20">
+        <v>422.0</v>
+      </c>
+      <c r="D120" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" s="28">
+        <v>5000.0</v>
+      </c>
+      <c r="F120" s="23">
+        <v>1.036E7</v>
+      </c>
+      <c r="G120" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="H120" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B121" s="19" t="s">
+      <c r="A121" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B121" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C121" s="20">
+      <c r="C121" s="37">
         <v>422.0</v>
       </c>
-      <c r="D121" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="E121" s="27">
-        <v>5000.0</v>
-      </c>
-      <c r="F121" s="22">
-        <v>1.036E7</v>
-      </c>
-      <c r="G121" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="H121" s="28" t="s">
+      <c r="D121" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E121" s="35">
+        <v>589560.0</v>
+      </c>
+      <c r="F121" s="36">
+        <v>1.147E7</v>
+      </c>
+      <c r="G121" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="H121" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B122" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="C122" s="36">
-        <v>422.0</v>
-      </c>
-      <c r="D122" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="E122" s="34">
-        <v>589560.0</v>
-      </c>
-      <c r="F122" s="35">
-        <v>1.147E7</v>
-      </c>
-      <c r="G122" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="H122" s="28" t="s">
-        <v>45</v>
+      <c r="A122" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B122" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C122" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D122" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E122" s="38">
+        <v>1000.0</v>
+      </c>
+      <c r="F122" s="36">
+        <v>1.058E7</v>
+      </c>
+      <c r="G122" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="H122" s="29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B123" s="31" t="s">
+      <c r="A123" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B123" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C123" s="36">
+      <c r="C123" s="37">
         <v>451.0</v>
       </c>
-      <c r="D123" s="33" t="s">
+      <c r="D123" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="E123" s="37">
+      <c r="E123" s="38">
+        <v>9362139.29</v>
+      </c>
+      <c r="F123" s="36">
+        <v>1.059E7</v>
+      </c>
+      <c r="G123" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="H123" s="29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B124" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C124" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D124" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E124" s="38">
+        <v>3.49143533E7</v>
+      </c>
+      <c r="F124" s="36">
+        <v>1.06E7</v>
+      </c>
+      <c r="G124" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="H124" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B125" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C125" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D125" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E125" s="38">
+        <v>1001000.0</v>
+      </c>
+      <c r="F125" s="36">
+        <v>1.061E7</v>
+      </c>
+      <c r="G125" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="H125" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B126" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C126" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D126" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E126" s="38">
         <v>1000.0</v>
       </c>
-      <c r="F123" s="35">
-        <v>1.058E7</v>
-      </c>
-      <c r="G123" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="H123" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B124" s="31" t="s">
+      <c r="F126" s="36">
+        <v>1.34E7</v>
+      </c>
+      <c r="G126" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="H126" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B127" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C124" s="36">
+      <c r="C127" s="37">
         <v>451.0</v>
       </c>
-      <c r="D124" s="33" t="s">
+      <c r="D127" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="E124" s="37">
-        <v>9362139.29</v>
-      </c>
-      <c r="F124" s="35">
+      <c r="E127" s="38">
+        <v>1000.0</v>
+      </c>
+      <c r="F127" s="36">
+        <v>2.306E7</v>
+      </c>
+      <c r="G127" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="H127" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B128" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C128" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D128" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E128" s="38">
+        <v>3295000.0</v>
+      </c>
+      <c r="F128" s="36">
+        <v>1.099E7</v>
+      </c>
+      <c r="G128" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="H128" s="29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B129" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C129" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D129" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E129" s="38">
+        <v>33.52</v>
+      </c>
+      <c r="F129" s="36">
+        <v>2.201E7</v>
+      </c>
+      <c r="G129" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="H129" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C130" s="20">
+        <v>451.0</v>
+      </c>
+      <c r="D130" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E130" s="28">
+        <v>1000.0</v>
+      </c>
+      <c r="F130" s="23">
         <v>1.059E7</v>
       </c>
-      <c r="G124" s="35" t="s">
+      <c r="G130" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="H124" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B125" s="31" t="s">
+      <c r="H130" s="29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B131" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C125" s="36">
+      <c r="C131" s="37">
         <v>451.0</v>
       </c>
-      <c r="D125" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E125" s="37">
-        <v>3.49143533E7</v>
-      </c>
-      <c r="F125" s="35">
-        <v>1.06E7</v>
-      </c>
-      <c r="G125" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="H125" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B126" s="31" t="s">
+      <c r="D131" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E131" s="38">
+        <v>1.78625E7</v>
+      </c>
+      <c r="F131" s="36">
+        <v>1.097E7</v>
+      </c>
+      <c r="G131" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H131" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B132" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C126" s="36">
+      <c r="C132" s="37">
         <v>451.0</v>
       </c>
-      <c r="D126" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E126" s="37">
-        <v>1001000.0</v>
-      </c>
-      <c r="F126" s="35">
-        <v>1.061E7</v>
-      </c>
-      <c r="G126" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="H126" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B127" s="31" t="s">
+      <c r="D132" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E132" s="38">
+        <v>9938000.0</v>
+      </c>
+      <c r="F132" s="36">
+        <v>1.098E7</v>
+      </c>
+      <c r="G132" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="H132" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B133" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C127" s="36">
+      <c r="C133" s="37">
         <v>451.0</v>
       </c>
-      <c r="D127" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E127" s="37">
-        <v>1000.0</v>
-      </c>
-      <c r="F127" s="35">
-        <v>1.34E7</v>
-      </c>
-      <c r="G127" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="H127" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B128" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C128" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D128" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E128" s="37">
-        <v>1000.0</v>
-      </c>
-      <c r="F128" s="35">
-        <v>2.306E7</v>
-      </c>
-      <c r="G128" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="H128" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B129" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C129" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D129" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="E129" s="37">
-        <v>3295000.0</v>
-      </c>
-      <c r="F129" s="35">
-        <v>1.099E7</v>
-      </c>
-      <c r="G129" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="H129" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B130" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C130" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D130" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="E130" s="37">
-        <v>33.52</v>
-      </c>
-      <c r="F130" s="35">
-        <v>2.201E7</v>
-      </c>
-      <c r="G130" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="H130" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B131" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C131" s="20">
-        <v>451.0</v>
-      </c>
-      <c r="D131" s="20" t="s">
+      <c r="D133" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="E131" s="27">
-        <v>1000.0</v>
-      </c>
-      <c r="F131" s="22">
-        <v>1.059E7</v>
-      </c>
-      <c r="G131" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="H131" s="28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B132" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C132" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D132" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E132" s="37">
-        <v>1.78625E7</v>
-      </c>
-      <c r="F132" s="35">
-        <v>1.097E7</v>
-      </c>
-      <c r="G132" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="H132" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B133" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C133" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D133" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E133" s="37">
-        <v>9938000.0</v>
-      </c>
-      <c r="F133" s="35">
-        <v>1.098E7</v>
-      </c>
-      <c r="G133" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="H133" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B134" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C134" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D134" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E134" s="37">
+      <c r="E133" s="38">
         <f>4800000+3600000+9000000</f>
         <v>17400000</v>
       </c>
-      <c r="F134" s="35">
+      <c r="F133" s="36">
         <v>1.099E7</v>
       </c>
-      <c r="G134" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="H134" s="28" t="s">
-        <v>12</v>
+      <c r="G133" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="H133" s="29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B134" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C134" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D134" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E134" s="38">
+        <v>5705000.0</v>
+      </c>
+      <c r="F134" s="36">
+        <v>1.1E7</v>
+      </c>
+      <c r="G134" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="H134" s="29" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B135" s="31" t="s">
+      <c r="A135" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B135" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C135" s="36">
+      <c r="C135" s="37">
         <v>451.0</v>
       </c>
-      <c r="D135" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E135" s="37">
-        <v>5705000.0</v>
-      </c>
-      <c r="F135" s="35">
-        <v>1.1E7</v>
-      </c>
-      <c r="G135" s="35" t="s">
+      <c r="D135" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E135" s="38">
+        <v>1.0E7</v>
+      </c>
+      <c r="F135" s="36">
+        <v>1.331E7</v>
+      </c>
+      <c r="G135" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="H135" s="28" t="s">
+      <c r="H135" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B136" s="31" t="s">
+      <c r="A136" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B136" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C136" s="36">
+      <c r="C136" s="37">
         <v>451.0</v>
       </c>
-      <c r="D136" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E136" s="37">
-        <v>1.0E7</v>
-      </c>
-      <c r="F136" s="35">
-        <v>1.331E7</v>
-      </c>
-      <c r="G136" s="35" t="s">
+      <c r="D136" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E136" s="38">
+        <v>1.6034E7</v>
+      </c>
+      <c r="F136" s="36">
+        <v>2.142E7</v>
+      </c>
+      <c r="G136" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="H136" s="28" t="s">
+      <c r="H136" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B137" s="31" t="s">
+      <c r="A137" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B137" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C137" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D137" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E137" s="37">
-        <v>1.6034E7</v>
-      </c>
-      <c r="F137" s="35">
-        <v>2.142E7</v>
-      </c>
-      <c r="G137" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="H137" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B138" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C138" s="36">
+      <c r="C137" s="37">
         <v>512.0</v>
       </c>
-      <c r="D138" s="33" t="s">
+      <c r="D137" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="E138" s="39">
+      <c r="E137" s="40">
         <f>3000</f>
         <v>3000</v>
       </c>
-      <c r="F138" s="35">
+      <c r="F137" s="36">
         <v>1.337E7</v>
       </c>
-      <c r="G138" s="35" t="s">
+      <c r="G137" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H137" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B138" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="H138" s="28" t="s">
+      <c r="C138" s="37">
+        <v>122.0</v>
+      </c>
+      <c r="D138" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E138" s="38">
+        <v>150000.0</v>
+      </c>
+      <c r="F138" s="36">
+        <v>2.275E7</v>
+      </c>
+      <c r="G138" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="H138" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B139" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C139" s="36">
-        <v>122.0</v>
-      </c>
-      <c r="D139" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="E139" s="37">
-        <v>150000.0</v>
-      </c>
-      <c r="F139" s="35">
-        <v>2.275E7</v>
-      </c>
-      <c r="G139" s="35" t="s">
+      <c r="A139" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C139" s="20">
+        <v>482.0</v>
+      </c>
+      <c r="D139" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="H139" s="28" t="s">
+      <c r="E139" s="28">
+        <v>100000.0</v>
+      </c>
+      <c r="F139" s="23">
+        <v>1.057E7</v>
+      </c>
+      <c r="G139" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H139" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B140" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C140" s="20">
+      <c r="A140" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B140" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C140" s="37">
         <v>482.0</v>
       </c>
-      <c r="D140" s="20" t="s">
+      <c r="D140" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E140" s="41">
+        <v>7541842.2</v>
+      </c>
+      <c r="F140" s="36">
+        <v>1.057E7</v>
+      </c>
+      <c r="G140" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="E140" s="27">
-        <v>100000.0</v>
-      </c>
-      <c r="F140" s="22">
-        <v>1.057E7</v>
-      </c>
-      <c r="G140" s="22" t="s">
+      <c r="H140" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B141" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="H140" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B141" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C141" s="36">
-        <v>482.0</v>
-      </c>
-      <c r="D141" s="33" t="s">
+      <c r="C141" s="37">
+        <v>512.0</v>
+      </c>
+      <c r="D141" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="E141" s="40">
-        <v>7541842.2</v>
-      </c>
-      <c r="F141" s="35">
-        <v>1.057E7</v>
-      </c>
-      <c r="G141" s="35" t="s">
+      <c r="E141" s="38">
+        <v>3000.0</v>
+      </c>
+      <c r="F141" s="36">
+        <v>1.338E7</v>
+      </c>
+      <c r="G141" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="H141" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B142" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="H141" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B142" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="C142" s="36">
+      <c r="C142" s="20">
         <v>512.0</v>
       </c>
-      <c r="D142" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E142" s="37">
-        <v>3000.0</v>
-      </c>
-      <c r="F142" s="35">
-        <v>1.338E7</v>
-      </c>
-      <c r="G142" s="35" t="s">
+      <c r="D142" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E142" s="22">
+        <v>3221000.0</v>
+      </c>
+      <c r="F142" s="23">
+        <v>1.101E7</v>
+      </c>
+      <c r="G142" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="H142" s="28" t="s">
+      <c r="H142" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C143" s="20">
         <v>512.0</v>
       </c>
-      <c r="D143" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E143" s="21">
-        <v>3221000.0</v>
-      </c>
-      <c r="F143" s="22">
-        <v>1.101E7</v>
-      </c>
-      <c r="G143" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="H143" s="28" t="s">
+      <c r="D143" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E143" s="22">
+        <v>1000000.0</v>
+      </c>
+      <c r="F143" s="23">
+        <v>1.102E7</v>
+      </c>
+      <c r="G143" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="H143" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C144" s="20">
         <v>512.0</v>
       </c>
-      <c r="D144" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E144" s="21">
+      <c r="D144" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E144" s="22">
+        <v>8550000.0</v>
+      </c>
+      <c r="F144" s="23">
+        <v>1.103E7</v>
+      </c>
+      <c r="G144" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="H144" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B145" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C145" s="37">
+        <v>512.0</v>
+      </c>
+      <c r="D145" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E145" s="38">
+        <v>6030000.0</v>
+      </c>
+      <c r="F145" s="36">
+        <v>1.129E7</v>
+      </c>
+      <c r="G145" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="H145" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B146" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C146" s="37">
+        <v>512.0</v>
+      </c>
+      <c r="D146" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E146" s="38">
+        <v>799000.0</v>
+      </c>
+      <c r="F146" s="36">
+        <v>1130000.0</v>
+      </c>
+      <c r="G146" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="H146" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C147" s="20">
+        <v>512.0</v>
+      </c>
+      <c r="D147" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E147" s="28">
+        <v>325000.0</v>
+      </c>
+      <c r="F147" s="23">
+        <v>1.045E7</v>
+      </c>
+      <c r="G147" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="H147" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B148" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C148" s="37">
+        <v>122.0</v>
+      </c>
+      <c r="D148" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="35">
+        <v>1000.0</v>
+      </c>
+      <c r="F148" s="36">
+        <v>2.163E7</v>
+      </c>
+      <c r="G148" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H148" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C149" s="20">
+        <v>542.0</v>
+      </c>
+      <c r="D149" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E149" s="28">
+        <v>1000.0</v>
+      </c>
+      <c r="F149" s="23">
+        <v>1.138E7</v>
+      </c>
+      <c r="G149" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="H149" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C150" s="37">
+        <v>571.0</v>
+      </c>
+      <c r="D150" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="E150" s="35">
+        <v>10.0</v>
+      </c>
+      <c r="F150" s="36">
+        <v>1.156E7</v>
+      </c>
+      <c r="G150" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="H150" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" s="20">
+        <v>451.0</v>
+      </c>
+      <c r="D151" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E151" s="28">
         <v>1000000.0</v>
       </c>
-      <c r="F144" s="22">
-        <v>1.102E7</v>
-      </c>
-      <c r="G144" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="H144" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C145" s="20">
-        <v>512.0</v>
-      </c>
-      <c r="D145" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E145" s="21">
-        <v>8550000.0</v>
-      </c>
-      <c r="F145" s="22">
-        <v>1.103E7</v>
-      </c>
-      <c r="G145" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="H145" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B146" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="C146" s="36">
-        <v>512.0</v>
-      </c>
-      <c r="D146" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="E146" s="37">
-        <v>6030000.0</v>
-      </c>
-      <c r="F146" s="35">
-        <v>1.129E7</v>
-      </c>
-      <c r="G146" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="H146" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B147" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="C147" s="36">
-        <v>512.0</v>
-      </c>
-      <c r="D147" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="E147" s="37">
-        <v>799000.0</v>
-      </c>
-      <c r="F147" s="35">
-        <v>1130000.0</v>
-      </c>
-      <c r="G147" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="H147" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B148" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C148" s="20">
-        <v>512.0</v>
-      </c>
-      <c r="D148" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E148" s="27">
-        <v>325000.0</v>
-      </c>
-      <c r="F148" s="22">
-        <v>1.045E7</v>
-      </c>
-      <c r="G148" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="H148" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B149" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C149" s="36">
-        <v>122.0</v>
-      </c>
-      <c r="D149" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="E149" s="34">
-        <v>1000.0</v>
-      </c>
-      <c r="F149" s="35">
-        <v>2.163E7</v>
-      </c>
-      <c r="G149" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="H149" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B150" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C150" s="20">
-        <v>542.0</v>
-      </c>
-      <c r="D150" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E150" s="27">
-        <v>1000.0</v>
-      </c>
-      <c r="F150" s="22">
-        <v>1.138E7</v>
-      </c>
-      <c r="G150" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="H150" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B151" s="31" t="s">
+      <c r="F151" s="23">
+        <v>1.084E7</v>
+      </c>
+      <c r="G151" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C151" s="36">
-        <v>571.0</v>
-      </c>
-      <c r="D151" s="33" t="s">
+      <c r="H151" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B152" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D152" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="E151" s="34">
-        <v>10.0</v>
-      </c>
-      <c r="F151" s="35">
-        <v>1.156E7</v>
-      </c>
-      <c r="G151" s="35" t="s">
+      <c r="E152" s="35">
+        <v>2000000.0</v>
+      </c>
+      <c r="F152" s="36">
+        <v>1.073E7</v>
+      </c>
+      <c r="G152" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="H151" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B152" s="19" t="s">
+      <c r="H152" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B153" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C152" s="20">
-        <v>451.0</v>
-      </c>
-      <c r="D152" s="20" t="s">
+      <c r="C153" s="37">
+        <v>608.0</v>
+      </c>
+      <c r="D153" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E152" s="27">
-        <v>1000000.0</v>
-      </c>
-      <c r="F152" s="22">
-        <v>1.084E7</v>
-      </c>
-      <c r="G152" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="H152" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B153" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C153" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D153" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="E153" s="34">
-        <v>2000000.0</v>
-      </c>
-      <c r="F153" s="35">
-        <v>1.073E7</v>
-      </c>
-      <c r="G153" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="H153" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B154" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C154" s="36">
-        <v>608.0</v>
-      </c>
-      <c r="D154" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E154" s="34">
+      <c r="E153" s="35">
         <f>3100000</f>
         <v>3100000</v>
       </c>
-      <c r="F154" s="35">
+      <c r="F153" s="36">
         <v>1.079E7</v>
       </c>
-      <c r="G154" s="35" t="s">
+      <c r="G153" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="H154" s="28" t="s">
+      <c r="H153" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B154" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" s="37">
+        <v>608.0</v>
+      </c>
+      <c r="D154" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E154" s="38">
+        <v>1000.0</v>
+      </c>
+      <c r="F154" s="36">
+        <v>1.081E7</v>
+      </c>
+      <c r="G154" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H154" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B155" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C155" s="36">
-        <v>608.0</v>
-      </c>
-      <c r="D155" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E155" s="37">
+      <c r="A155" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B155" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C155" s="37">
+        <v>127.0</v>
+      </c>
+      <c r="D155" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="E155" s="38">
         <v>1000.0</v>
       </c>
-      <c r="F155" s="35">
-        <v>1.081E7</v>
-      </c>
-      <c r="G155" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="H155" s="28" t="s">
+      <c r="F155" s="36">
+        <v>1.339E7</v>
+      </c>
+      <c r="G155" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="H155" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B156" s="31" t="s">
+      <c r="A156" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C156" s="37">
+        <v>122.0</v>
+      </c>
+      <c r="D156" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E156" s="35">
+        <v>335.17</v>
+      </c>
+      <c r="F156" s="36">
+        <v>2.203E7</v>
+      </c>
+      <c r="G156" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="C156" s="36">
-        <v>127.0</v>
-      </c>
-      <c r="D156" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="E156" s="37">
-        <v>1000.0</v>
-      </c>
-      <c r="F156" s="35">
-        <v>1.339E7</v>
-      </c>
-      <c r="G156" s="35" t="s">
+      <c r="H156" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B157" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C157" s="37">
+        <v>451.0</v>
+      </c>
+      <c r="D157" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E157" s="35">
+        <v>368.69</v>
+      </c>
+      <c r="F157" s="36">
+        <v>1.171E7</v>
+      </c>
+      <c r="G157" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="H156" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B157" s="31" t="s">
+      <c r="H157" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B158" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C158" s="37">
+        <v>781.0</v>
+      </c>
+      <c r="D158" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E158" s="35">
+        <v>750308.03</v>
+      </c>
+      <c r="F158" s="36">
+        <v>1.168E7</v>
+      </c>
+      <c r="G158" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="C157" s="36">
-        <v>122.0</v>
-      </c>
-      <c r="D157" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E157" s="34">
+      <c r="H158" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B159" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C159" s="37">
+        <v>782.0</v>
+      </c>
+      <c r="D159" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E159" s="38">
+        <v>33.52</v>
+      </c>
+      <c r="F159" s="36">
+        <v>1.169E7</v>
+      </c>
+      <c r="G159" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="H159" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B160" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C160" s="37">
+        <v>782.0</v>
+      </c>
+      <c r="D160" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E160" s="38">
+        <v>5.753131818E7</v>
+      </c>
+      <c r="F160" s="36">
+        <v>2.196E7</v>
+      </c>
+      <c r="G160" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="H160" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B161" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C161" s="37">
+        <v>782.0</v>
+      </c>
+      <c r="D161" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E161" s="38">
+        <v>9541877.72</v>
+      </c>
+      <c r="F161" s="36">
+        <v>2.197E7</v>
+      </c>
+      <c r="G161" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="H161" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C162" s="37">
+        <v>782.0</v>
+      </c>
+      <c r="D162" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E162" s="38">
+        <v>3.330026246E7</v>
+      </c>
+      <c r="F162" s="36">
+        <v>2.198E7</v>
+      </c>
+      <c r="G162" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="H162" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B163" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C163" s="37">
+        <v>782.0</v>
+      </c>
+      <c r="D163" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E163" s="38">
+        <v>33516.79</v>
+      </c>
+      <c r="F163" s="36">
+        <v>2.199E7</v>
+      </c>
+      <c r="G163" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="H163" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B164" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C164" s="37">
+        <v>782.0</v>
+      </c>
+      <c r="D164" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E164" s="38">
         <v>335.17</v>
       </c>
-      <c r="F157" s="35">
-        <v>2.203E7</v>
-      </c>
-      <c r="G157" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="H157" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B158" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C158" s="36">
-        <v>451.0</v>
-      </c>
-      <c r="D158" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E158" s="34">
-        <v>368.69</v>
-      </c>
-      <c r="F158" s="35">
-        <v>1.171E7</v>
-      </c>
-      <c r="G158" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="H158" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B159" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C159" s="36">
-        <v>781.0</v>
-      </c>
-      <c r="D159" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E159" s="34">
-        <v>750308.03</v>
-      </c>
-      <c r="F159" s="35">
-        <v>1.168E7</v>
-      </c>
-      <c r="G159" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="H159" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B160" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C160" s="36">
-        <v>782.0</v>
-      </c>
-      <c r="D160" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E160" s="37">
-        <v>33.52</v>
-      </c>
-      <c r="F160" s="35">
-        <v>1.169E7</v>
-      </c>
-      <c r="G160" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H160" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B161" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C161" s="36">
-        <v>782.0</v>
-      </c>
-      <c r="D161" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E161" s="37">
-        <v>5.753131818E7</v>
-      </c>
-      <c r="F161" s="35">
-        <v>2.196E7</v>
-      </c>
-      <c r="G161" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="H161" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B162" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C162" s="36">
-        <v>782.0</v>
-      </c>
-      <c r="D162" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E162" s="37">
-        <v>9541877.72</v>
-      </c>
-      <c r="F162" s="35">
-        <v>2.197E7</v>
-      </c>
-      <c r="G162" s="35" t="s">
+      <c r="F164" s="36">
+        <v>2.2E7</v>
+      </c>
+      <c r="G164" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="H162" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B163" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C163" s="36">
-        <v>782.0</v>
-      </c>
-      <c r="D163" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E163" s="37">
-        <v>3.330026246E7</v>
-      </c>
-      <c r="F163" s="35">
-        <v>2.198E7</v>
-      </c>
-      <c r="G163" s="35" t="s">
+      <c r="H164" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B165" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="H163" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B164" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C164" s="36">
-        <v>782.0</v>
-      </c>
-      <c r="D164" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E164" s="37">
-        <v>33516.79</v>
-      </c>
-      <c r="F164" s="35">
-        <v>2.199E7</v>
-      </c>
-      <c r="G164" s="35" t="s">
+      <c r="C165" s="37">
+        <v>812.0</v>
+      </c>
+      <c r="D165" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="H164" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B165" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="C165" s="36">
-        <v>782.0</v>
-      </c>
-      <c r="D165" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E165" s="37">
-        <v>335.17</v>
-      </c>
-      <c r="F165" s="35">
-        <v>2.2E7</v>
-      </c>
-      <c r="G165" s="35" t="s">
+      <c r="E165" s="35">
+        <v>4466051.73</v>
+      </c>
+      <c r="F165" s="36">
+        <v>1.332E7</v>
+      </c>
+      <c r="G165" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="H165" s="28" t="s">
+      <c r="H165" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B166" s="31" t="s">
+      <c r="F166" s="43"/>
+      <c r="G166" s="18"/>
+      <c r="H166" s="18"/>
+    </row>
+    <row r="167" ht="22.5" customHeight="1">
+      <c r="A167" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H167" s="18"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="C166" s="36">
-        <v>812.0</v>
-      </c>
-      <c r="D166" s="33" t="s">
+      <c r="B168" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="E166" s="34">
-        <v>4466051.73</v>
-      </c>
-      <c r="F166" s="35">
-        <v>1.332E7</v>
-      </c>
-      <c r="G166" s="35" t="s">
+      <c r="C168" s="20">
+        <v>244.0</v>
+      </c>
+      <c r="D168" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E168" s="22">
+        <v>79000.0</v>
+      </c>
+      <c r="F168" s="23">
+        <v>1.222E7</v>
+      </c>
+      <c r="G168" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="H166" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="F167" s="44"/>
-      <c r="G167" s="18"/>
-      <c r="H167" s="18"/>
-    </row>
-    <row r="168" ht="22.5" customHeight="1">
-      <c r="A168" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H168" s="18"/>
+      <c r="H168" s="25" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B169" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C169" s="20">
         <v>244.0</v>
       </c>
-      <c r="D169" s="20" t="s">
+      <c r="D169" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E169" s="21">
-        <v>79000.0</v>
-      </c>
-      <c r="F169" s="22">
-        <v>1.222E7</v>
-      </c>
-      <c r="G169" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="H169" s="24" t="s">
+      <c r="E169" s="22">
+        <v>1000000.0</v>
+      </c>
+      <c r="F169" s="23">
+        <v>1.236E7</v>
+      </c>
+      <c r="G169" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="H169" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B170" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C170" s="20">
         <v>244.0</v>
       </c>
-      <c r="D170" s="20" t="s">
+      <c r="D170" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E170" s="21">
-        <v>1000000.0</v>
-      </c>
-      <c r="F170" s="22">
-        <v>1.236E7</v>
-      </c>
-      <c r="G170" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="H170" s="24" t="s">
+      <c r="E170" s="22">
+        <v>69000.0</v>
+      </c>
+      <c r="F170" s="23">
+        <v>1.254E7</v>
+      </c>
+      <c r="G170" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="H170" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B171" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C171" s="20">
         <v>244.0</v>
       </c>
-      <c r="D171" s="20" t="s">
+      <c r="D171" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E171" s="21">
-        <v>69000.0</v>
-      </c>
-      <c r="F171" s="22">
-        <v>1.254E7</v>
-      </c>
-      <c r="G171" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="H171" s="24" t="s">
-        <v>45</v>
+      <c r="E171" s="22">
+        <v>800000.0</v>
+      </c>
+      <c r="F171" s="23">
+        <v>1.266E7</v>
+      </c>
+      <c r="G171" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="H171" s="25" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C172" s="20">
         <v>244.0</v>
       </c>
-      <c r="D172" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E172" s="21">
-        <v>800000.0</v>
-      </c>
-      <c r="F172" s="22">
-        <v>1.266E7</v>
-      </c>
-      <c r="G172" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="H172" s="24" t="s">
+      <c r="D172" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E172" s="22">
+        <v>529000.0</v>
+      </c>
+      <c r="F172" s="23">
+        <v>1.249E7</v>
+      </c>
+      <c r="G172" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="H172" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B173" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C173" s="20">
         <v>244.0</v>
       </c>
-      <c r="D173" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="E173" s="21">
-        <v>529000.0</v>
-      </c>
-      <c r="F173" s="22">
-        <v>1.249E7</v>
-      </c>
-      <c r="G173" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="H173" s="28" t="s">
+      <c r="D173" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E173" s="22">
+        <v>50000.0</v>
+      </c>
+      <c r="F173" s="23">
+        <v>1.266E7</v>
+      </c>
+      <c r="G173" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="H173" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B174" s="19" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C174" s="20">
-        <v>244.0</v>
-      </c>
-      <c r="D174" s="20" t="s">
+        <v>422.0</v>
+      </c>
+      <c r="D174" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E174" s="28">
+        <v>65200.0</v>
+      </c>
+      <c r="F174" s="23">
+        <v>1.043E7</v>
+      </c>
+      <c r="G174" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="E174" s="21">
-        <v>50000.0</v>
-      </c>
-      <c r="F174" s="22">
-        <v>1.266E7</v>
-      </c>
-      <c r="G174" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="H174" s="28" t="s">
-        <v>12</v>
+      <c r="H174" s="25" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B175" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C175" s="20">
         <v>422.0</v>
       </c>
-      <c r="D175" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="E175" s="27">
-        <v>65200.0</v>
-      </c>
-      <c r="F175" s="22">
-        <v>1.043E7</v>
-      </c>
-      <c r="G175" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="H175" s="24" t="s">
+      <c r="D175" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E175" s="28">
+        <v>580000.0</v>
+      </c>
+      <c r="F175" s="23">
+        <v>1.223E7</v>
+      </c>
+      <c r="G175" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H175" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B176" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C176" s="20">
         <v>422.0</v>
       </c>
-      <c r="D176" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E176" s="27">
-        <v>580000.0</v>
-      </c>
-      <c r="F176" s="22">
-        <v>1.223E7</v>
-      </c>
-      <c r="G176" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="H176" s="24" t="s">
+      <c r="D176" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E176" s="22">
+        <v>178000.0</v>
+      </c>
+      <c r="F176" s="23">
+        <v>1.027E7</v>
+      </c>
+      <c r="G176" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="H176" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B177" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C177" s="20">
         <v>422.0</v>
       </c>
-      <c r="D177" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="E177" s="21">
-        <v>178000.0</v>
-      </c>
-      <c r="F177" s="22">
-        <v>1.027E7</v>
-      </c>
-      <c r="G177" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="H177" s="24" t="s">
+      <c r="D177" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E177" s="22">
+        <v>71000.0</v>
+      </c>
+      <c r="F177" s="23">
+        <v>1.028E7</v>
+      </c>
+      <c r="G177" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="H177" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B178" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C178" s="20">
         <v>422.0</v>
       </c>
-      <c r="D178" s="20" t="s">
+      <c r="D178" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E178" s="22">
+        <v>321000.0</v>
+      </c>
+      <c r="F178" s="23">
+        <v>1.029E7</v>
+      </c>
+      <c r="G178" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="E178" s="21">
-        <v>71000.0</v>
-      </c>
-      <c r="F178" s="22">
-        <v>1.028E7</v>
-      </c>
-      <c r="G178" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="H178" s="24" t="s">
+      <c r="H178" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C179" s="20">
         <v>422.0</v>
       </c>
-      <c r="D179" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="E179" s="21">
-        <v>321000.0</v>
-      </c>
-      <c r="F179" s="22">
-        <v>1.029E7</v>
-      </c>
-      <c r="G179" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="H179" s="24" t="s">
+      <c r="D179" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E179" s="22">
+        <v>221000.0</v>
+      </c>
+      <c r="F179" s="23">
+        <v>1.03E7</v>
+      </c>
+      <c r="G179" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="H179" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B180" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C180" s="20">
         <v>422.0</v>
       </c>
-      <c r="D180" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="E180" s="21">
-        <v>221000.0</v>
-      </c>
-      <c r="F180" s="22">
-        <v>1.03E7</v>
-      </c>
-      <c r="G180" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="H180" s="24" t="s">
+      <c r="D180" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E180" s="22">
+        <v>4048000.0</v>
+      </c>
+      <c r="F180" s="23">
+        <v>2.083E7</v>
+      </c>
+      <c r="G180" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="H180" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B181" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C181" s="20">
         <v>422.0</v>
       </c>
-      <c r="D181" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="E181" s="21">
-        <v>4048000.0</v>
-      </c>
-      <c r="F181" s="22">
-        <v>2.083E7</v>
-      </c>
-      <c r="G181" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="H181" s="24" t="s">
+      <c r="D181" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E181" s="28">
+        <v>1030000.0</v>
+      </c>
+      <c r="F181" s="23">
+        <v>1.035E7</v>
+      </c>
+      <c r="G181" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="H181" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B182" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C182" s="20">
         <v>422.0</v>
       </c>
-      <c r="D182" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="E182" s="27">
-        <v>1030000.0</v>
-      </c>
-      <c r="F182" s="22">
-        <v>1.035E7</v>
-      </c>
-      <c r="G182" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="H182" s="24" t="s">
+      <c r="D182" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E182" s="28">
+        <f>2415560-1937560</f>
+        <v>478000</v>
+      </c>
+      <c r="F182" s="23">
+        <v>1.146E7</v>
+      </c>
+      <c r="G182" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="H182" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B183" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C183" s="20">
-        <v>422.0</v>
-      </c>
-      <c r="D183" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="E183" s="27">
-        <f>2415560-1937560</f>
-        <v>478000</v>
-      </c>
-      <c r="F183" s="22">
-        <v>1.146E7</v>
-      </c>
-      <c r="G183" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="H183" s="24" t="s">
-        <v>45</v>
+        <v>423.0</v>
+      </c>
+      <c r="D183" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E183" s="22">
+        <v>2000.0</v>
+      </c>
+      <c r="F183" s="23">
+        <v>1.086E7</v>
+      </c>
+      <c r="G183" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="H183" s="29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B184" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C184" s="20">
         <v>423.0</v>
       </c>
-      <c r="D184" s="20" t="s">
+      <c r="D184" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="E184" s="21">
+      <c r="E184" s="22">
         <v>2000.0</v>
       </c>
-      <c r="F184" s="22">
-        <v>1.086E7</v>
-      </c>
-      <c r="G184" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="H184" s="28" t="s">
+      <c r="F184" s="23">
+        <v>1.087E7</v>
+      </c>
+      <c r="G184" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="H184" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B185" s="19" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="C185" s="20">
-        <v>423.0</v>
-      </c>
-      <c r="D185" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E185" s="21">
-        <v>2000.0</v>
-      </c>
-      <c r="F185" s="22">
-        <v>1.087E7</v>
-      </c>
-      <c r="G185" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="H185" s="28" t="s">
-        <v>12</v>
+        <v>127.0</v>
+      </c>
+      <c r="D185" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="E185" s="28">
+        <v>1151000.0</v>
+      </c>
+      <c r="F185" s="23">
+        <v>1.339E7</v>
+      </c>
+      <c r="G185" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="H185" s="25" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C186" s="20">
         <v>127.0</v>
       </c>
-      <c r="D186" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="E186" s="27">
-        <v>1151000.0</v>
-      </c>
-      <c r="F186" s="22">
-        <v>1.339E7</v>
-      </c>
-      <c r="G186" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="H186" s="24" t="s">
+      <c r="D186" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E186" s="22">
+        <v>797700.0</v>
+      </c>
+      <c r="F186" s="23">
+        <v>1.031E7</v>
+      </c>
+      <c r="G186" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="H186" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B187" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C187" s="20">
         <v>127.0</v>
       </c>
-      <c r="D187" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="E187" s="21">
-        <v>797700.0</v>
-      </c>
-      <c r="F187" s="22">
-        <v>1.031E7</v>
-      </c>
-      <c r="G187" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="H187" s="24" t="s">
+      <c r="D187" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E187" s="22">
+        <v>5156900.0</v>
+      </c>
+      <c r="F187" s="23">
+        <v>1.032E7</v>
+      </c>
+      <c r="G187" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="H187" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B188" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C188" s="20">
         <v>127.0</v>
       </c>
-      <c r="D188" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="E188" s="21">
-        <v>5156900.0</v>
-      </c>
-      <c r="F188" s="22">
-        <v>1.032E7</v>
-      </c>
-      <c r="G188" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="H188" s="24" t="s">
+      <c r="D188" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E188" s="22">
+        <v>102000.0</v>
+      </c>
+      <c r="F188" s="23">
+        <v>1.033E7</v>
+      </c>
+      <c r="G188" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="H188" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B189" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C189" s="20">
         <v>127.0</v>
       </c>
-      <c r="D189" s="20" t="s">
+      <c r="D189" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E189" s="22">
+        <v>20000.0</v>
+      </c>
+      <c r="F189" s="23">
+        <v>1.034E7</v>
+      </c>
+      <c r="G189" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="E189" s="21">
-        <v>102000.0</v>
-      </c>
-      <c r="F189" s="22">
-        <v>1.033E7</v>
-      </c>
-      <c r="G189" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="H189" s="24" t="s">
+      <c r="H189" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B190" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C190" s="20">
         <v>127.0</v>
       </c>
-      <c r="D190" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="E190" s="21">
-        <v>20000.0</v>
-      </c>
-      <c r="F190" s="22">
-        <v>1.034E7</v>
-      </c>
-      <c r="G190" s="22" t="s">
+      <c r="D190" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E190" s="22">
+        <v>6110535.52</v>
+      </c>
+      <c r="F190" s="23">
+        <v>2.084E7</v>
+      </c>
+      <c r="G190" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="H190" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="F191" s="17"/>
+      <c r="G191" s="18"/>
+      <c r="H191" s="18"/>
+    </row>
+    <row r="192" ht="22.5" customHeight="1">
+      <c r="A192" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B193" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="H190" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B191" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="C191" s="20">
-        <v>127.0</v>
-      </c>
-      <c r="D191" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="E191" s="21">
-        <v>6110535.52</v>
-      </c>
-      <c r="F191" s="22">
-        <v>2.084E7</v>
-      </c>
-      <c r="G191" s="22" t="s">
+      <c r="C193" s="20">
+        <v>124.0</v>
+      </c>
+      <c r="D193" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="H191" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="F192" s="17"/>
-      <c r="G192" s="18"/>
-      <c r="H192" s="18"/>
-    </row>
-    <row r="193" ht="22.5" customHeight="1">
-      <c r="A193" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H193" s="4" t="s">
-        <v>7</v>
+      <c r="E193" s="28">
+        <v>660000.0</v>
+      </c>
+      <c r="F193" s="23">
+        <v>1.085E7</v>
+      </c>
+      <c r="G193" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="H193" s="44" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="19" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B194" s="19" t="s">
-        <v>256</v>
+        <v>9</v>
       </c>
       <c r="C194" s="20">
-        <v>124.0</v>
-      </c>
-      <c r="D194" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="E194" s="27">
-        <v>660000.0</v>
-      </c>
-      <c r="F194" s="22">
-        <v>1.085E7</v>
-      </c>
-      <c r="G194" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="H194" s="45" t="s">
-        <v>45</v>
+        <v>541.0</v>
+      </c>
+      <c r="D194" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" s="28">
+        <v>11000.0</v>
+      </c>
+      <c r="F194" s="23">
+        <v>1.126E7</v>
+      </c>
+      <c r="G194" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="H194" s="44" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="19" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B195" s="19" t="s">
         <v>9</v>
@@ -6629,82 +6638,82 @@
       <c r="C195" s="20">
         <v>541.0</v>
       </c>
-      <c r="D195" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E195" s="27">
-        <v>11000.0</v>
-      </c>
-      <c r="F195" s="22">
-        <v>1.126E7</v>
-      </c>
-      <c r="G195" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="H195" s="45" t="s">
+      <c r="D195" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E195" s="28">
+        <v>3000.0</v>
+      </c>
+      <c r="F195" s="23">
+        <v>1.141E7</v>
+      </c>
+      <c r="G195" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="H195" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="B196" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C196" s="20">
-        <v>541.0</v>
-      </c>
-      <c r="D196" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E196" s="27">
-        <v>3000.0</v>
-      </c>
-      <c r="F196" s="22">
-        <v>1.141E7</v>
-      </c>
-      <c r="G196" s="46" t="s">
-        <v>259</v>
-      </c>
-      <c r="H196" s="45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="F197" s="17"/>
-      <c r="G197" s="18"/>
-      <c r="H197" s="18"/>
-    </row>
-    <row r="198" ht="22.5" customHeight="1">
-      <c r="A198" s="1" t="s">
+      <c r="F196" s="17"/>
+      <c r="G196" s="18"/>
+      <c r="H196" s="18"/>
+    </row>
+    <row r="197" ht="22.5" customHeight="1">
+      <c r="A197" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="B197" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C197" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="D197" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E198" s="2" t="s">
+      <c r="E197" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F198" s="3" t="s">
+      <c r="F197" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G198" s="3" t="s">
+      <c r="G197" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H198" s="4" t="s">
+      <c r="H197" s="4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B198" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C198" s="20">
+        <v>542.0</v>
+      </c>
+      <c r="D198" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E198" s="28">
+        <v>1000.0</v>
+      </c>
+      <c r="F198" s="23">
+        <v>1.135E7</v>
+      </c>
+      <c r="G198" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H198" s="25" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B199" s="19" t="s">
         <v>73</v>
@@ -6712,426 +6721,400 @@
       <c r="C199" s="20">
         <v>542.0</v>
       </c>
-      <c r="D199" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="E199" s="27">
+      <c r="D199" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E199" s="28">
         <v>1000.0</v>
       </c>
-      <c r="F199" s="22">
+      <c r="F199" s="23">
         <v>1.135E7</v>
       </c>
-      <c r="G199" s="22" t="s">
+      <c r="G199" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="H199" s="24" t="s">
+      <c r="H199" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B200" s="19" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C200" s="20">
-        <v>542.0</v>
-      </c>
-      <c r="D200" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E200" s="27">
-        <v>1000.0</v>
-      </c>
-      <c r="F200" s="22">
-        <v>1.135E7</v>
-      </c>
-      <c r="G200" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H200" s="24" t="s">
+        <v>571.0</v>
+      </c>
+      <c r="D200" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E200" s="28">
+        <v>60.0</v>
+      </c>
+      <c r="F200" s="23">
+        <v>1.156E7</v>
+      </c>
+      <c r="G200" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="H200" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B201" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C201" s="20">
+        <v>573.0</v>
+      </c>
+      <c r="D201" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="E201" s="22">
+        <v>1156486.0</v>
+      </c>
+      <c r="F201" s="23">
+        <v>1.219E7</v>
+      </c>
+      <c r="G201" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="B201" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="C201" s="20">
-        <v>571.0</v>
-      </c>
-      <c r="D201" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E201" s="27">
-        <v>60.0</v>
-      </c>
-      <c r="F201" s="22">
-        <v>1.156E7</v>
-      </c>
-      <c r="G201" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="H201" s="24" t="s">
+      <c r="H201" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B202" s="19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C202" s="20">
         <v>573.0</v>
       </c>
-      <c r="D202" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="E202" s="21">
-        <v>1156486.0</v>
-      </c>
-      <c r="F202" s="22">
-        <v>1.219E7</v>
-      </c>
-      <c r="G202" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="H202" s="24" t="s">
+      <c r="D202" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="E202" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="F202" s="23">
+        <v>1.22E7</v>
+      </c>
+      <c r="G202" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="H202" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B203" s="19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C203" s="20">
         <v>573.0</v>
       </c>
-      <c r="D203" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="E203" s="21">
+      <c r="D203" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="E203" s="22">
         <v>1.0</v>
       </c>
-      <c r="F203" s="22">
-        <v>1.22E7</v>
-      </c>
-      <c r="G203" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="H203" s="24" t="s">
+      <c r="F203" s="23">
+        <v>1.278E7</v>
+      </c>
+      <c r="G203" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="H203" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B204" s="19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C204" s="20">
         <v>573.0</v>
       </c>
-      <c r="D204" s="20" t="s">
+      <c r="D204" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="E204" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="F204" s="23">
+        <v>1.28E7</v>
+      </c>
+      <c r="G204" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="E204" s="21">
-        <v>1.0</v>
-      </c>
-      <c r="F204" s="22">
-        <v>1.278E7</v>
-      </c>
-      <c r="G204" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="H204" s="24" t="s">
+      <c r="H204" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B205" s="19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C205" s="20">
         <v>573.0</v>
       </c>
-      <c r="D205" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="E205" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="F205" s="22">
-        <v>1.28E7</v>
-      </c>
-      <c r="G205" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="H205" s="24" t="s">
+      <c r="D205" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E205" s="22">
+        <v>70000.0</v>
+      </c>
+      <c r="F205" s="23">
+        <v>1.341E7</v>
+      </c>
+      <c r="G205" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="H205" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B206" s="19" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C206" s="20">
         <v>573.0</v>
       </c>
-      <c r="D206" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="E206" s="21">
-        <v>70000.0</v>
-      </c>
-      <c r="F206" s="22">
-        <v>1.341E7</v>
-      </c>
-      <c r="G206" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="H206" s="24" t="s">
+      <c r="D206" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E206" s="22">
+        <v>270000.0</v>
+      </c>
+      <c r="F206" s="23">
+        <v>1.342E7</v>
+      </c>
+      <c r="G206" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="H206" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B207" s="19" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C207" s="20">
         <v>573.0</v>
       </c>
-      <c r="D207" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="E207" s="21">
-        <v>270000.0</v>
-      </c>
-      <c r="F207" s="22">
-        <v>1.342E7</v>
-      </c>
-      <c r="G207" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="H207" s="24" t="s">
+      <c r="D207" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E207" s="22">
+        <v>680000.0</v>
+      </c>
+      <c r="F207" s="23">
+        <v>1.343E7</v>
+      </c>
+      <c r="G207" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="H207" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B208" s="19" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C208" s="20">
         <v>573.0</v>
       </c>
-      <c r="D208" s="20" t="s">
+      <c r="D208" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E208" s="28">
+        <v>700050.0</v>
+      </c>
+      <c r="F208" s="23">
+        <v>1.158E7</v>
+      </c>
+      <c r="G208" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="H208" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="F209" s="17"/>
+      <c r="G209" s="18"/>
+      <c r="H209" s="18"/>
+    </row>
+    <row r="210" ht="22.5" customHeight="1">
+      <c r="A210" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="E208" s="21">
-        <v>680000.0</v>
-      </c>
-      <c r="F208" s="22">
-        <v>1.343E7</v>
-      </c>
-      <c r="G208" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="H208" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B209" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C209" s="20">
-        <v>573.0</v>
-      </c>
-      <c r="D209" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E209" s="27">
-        <v>700050.0</v>
-      </c>
-      <c r="F209" s="22">
-        <v>1.158E7</v>
-      </c>
-      <c r="G209" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="H209" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="F210" s="17"/>
-      <c r="G210" s="18"/>
-      <c r="H210" s="18"/>
-    </row>
-    <row r="211" ht="22.5" customHeight="1">
-      <c r="A211" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G211" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H211" s="4" t="s">
-        <v>7</v>
+      <c r="B211" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C211" s="20">
+        <v>182.0</v>
+      </c>
+      <c r="D211" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E211" s="22">
+        <v>4000.0</v>
+      </c>
+      <c r="F211" s="23">
+        <v>1.013E7</v>
+      </c>
+      <c r="G211" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="H211" s="25" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="19" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B212" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C212" s="20">
         <v>182.0</v>
       </c>
-      <c r="D212" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E212" s="21">
-        <v>4000.0</v>
-      </c>
-      <c r="F212" s="22">
-        <v>1.013E7</v>
-      </c>
-      <c r="G212" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="H212" s="24" t="s">
+      <c r="D212" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E212" s="22">
+        <v>589667.0</v>
+      </c>
+      <c r="F212" s="23">
+        <v>2.272E7</v>
+      </c>
+      <c r="G212" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="H212" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="19" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B213" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C213" s="20">
         <v>182.0</v>
       </c>
-      <c r="D213" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E213" s="21">
-        <v>589667.0</v>
-      </c>
-      <c r="F213" s="22">
-        <v>2.272E7</v>
-      </c>
-      <c r="G213" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="H213" s="24" t="s">
+      <c r="D213" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E213" s="28">
+        <v>1.7753E7</v>
+      </c>
+      <c r="F213" s="23">
+        <v>2.079E7</v>
+      </c>
+      <c r="G213" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="H213" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="19" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="B214" s="19" t="s">
-        <v>116</v>
+        <v>227</v>
       </c>
       <c r="C214" s="20">
-        <v>182.0</v>
-      </c>
-      <c r="D214" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E214" s="27">
-        <v>1.7753E7</v>
-      </c>
-      <c r="F214" s="22">
-        <v>2.079E7</v>
-      </c>
-      <c r="G214" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="H214" s="24" t="s">
-        <v>12</v>
+        <v>244.0</v>
+      </c>
+      <c r="D214" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E214" s="28">
+        <v>250000.0</v>
+      </c>
+      <c r="F214" s="23">
+        <v>1.242E7</v>
+      </c>
+      <c r="G214" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="H214" s="47" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B215" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="C215" s="20">
-        <v>244.0</v>
-      </c>
-      <c r="D215" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="E215" s="27">
-        <v>250000.0</v>
-      </c>
-      <c r="F215" s="22">
-        <v>1.242E7</v>
-      </c>
-      <c r="G215" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="H215" s="48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="F216" s="49"/>
+      <c r="F215" s="48"/>
     </row>
   </sheetData>
   <dataValidations>
     <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E31">
       <formula1>AND(ISNUMBER(E2),(NOT(OR(NOT(ISERROR(DATEVALUE(E2))), AND(ISNUMBER(E2), LEFT(CELL("format", E2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H31 H34:H69 H73:H166 H169:H191 H194:H196 H199:H209 H212:H215">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H31 H34:H69 H73:H165 H168:H190 H193:H195 H198:H208 H211:H214">
       <formula1>"Exclusivo,Não Exclusivo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ORCAMENTOS - PROGRAMAS.xlsx
+++ b/ORCAMENTOS - PROGRAMAS.xlsx
@@ -13,22 +13,23 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={0619dc93-171c-4da2-b441-412af1ac3113}</author>
-    <author>tc={2a7dcfa7-c60f-45b9-842b-040baa35e254}</author>
-    <author>tc={c04e08d9-b3a5-458c-a077-712e51e5ccf6}</author>
-    <author>tc={f06b32da-dd55-4e63-aef3-1f65e72a0c83}</author>
+    <author>tc={3db4590b-99b0-46f9-8e5c-535b09fd0c09}</author>
+    <author>tc={8244c2f2-4132-4074-9ca2-389a2fe912cd}</author>
+    <author>tc={8ba3ea41-de65-44d7-bcaf-e66d12b358bb}</author>
+    <author>tc={bbd46d50-5793-4f27-acbb-bf2b066df97a}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{0619dc93-171c-4da2-b441-412af1ac3113}" ref="A1">
+    <comment authorId="0" xr:uid="{3db4590b-99b0-46f9-8e5c-535b09fd0c09}" ref="A73">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	@luisalnr@gmail.com manter apenas no Eixo VI - linha 163 da planilha
+	Não apareceram os seguintes órgãos: TCE, TJAC, DPE, MPAC (estão listados na planilha anterior, mas não estão nesta) @luisalnr@gmail.com
+Assigned to luisalnr@gmail.com
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{2a7dcfa7-c60f-45b9-842b-040baa35e254}" ref="E68">
+    <comment authorId="1" xr:uid="{8244c2f2-4132-4074-9ca2-389a2fe912cd}" ref="E68">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -39,17 +40,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}" ref="A73">
+    <comment authorId="2" xr:uid="{8ba3ea41-de65-44d7-bcaf-e66d12b358bb}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Não apareceram os seguintes órgãos: TCE, TJAC, DPE, MPAC (estão listados na planilha anterior, mas não estão nesta) @luisalnr@gmail.com
-Assigned to luisalnr@gmail.com
+	@luisalnr@gmail.com manter apenas no Eixo VI - linha 163 da planilha
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{f06b32da-dd55-4e63-aef3-1f65e72a0c83}" ref="E73">
+    <comment authorId="3" xr:uid="{bbd46d50-5793-4f27-acbb-bf2b066df97a}" ref="E73">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="273">
   <si>
     <t>Eixo</t>
   </si>
@@ -97,7 +97,7 @@
     <t>18 – Gestão Ambiental</t>
   </si>
   <si>
-    <t>715/199 - SEFAZ</t>
+    <t>715/199 - SEFAZ (Departamento do Tesouro Estadual)</t>
   </si>
   <si>
     <t>PROSPECÇÃO DE MERCADO DA ECONOMIA
@@ -379,9 +379,6 @@
   </si>
   <si>
     <t>CONSTRUÇÃO, REFORMA E AMPLIAÇÃO DOS PRÉDIOS DA PGE.</t>
-  </si>
-  <si>
-    <t>715/199 - SEFAZ (Departamento do Tesouro Estadual)</t>
   </si>
   <si>
     <t>PROGRAMA ESTADUAL DE ENFRENTAMENTO ÀS DEMANDAS CONTINGENTES.</t>
@@ -1007,7 +1004,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1122,9 +1119,6 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -1259,22 +1253,22 @@
 
 <file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{b50e36b7-5e74-4168-ae7d-4022b894adff}">
+  <Task id="{7f02e35a-7017-4008-a94e-1ebb9b3b14da}">
     <Anchor>
-      <Comment id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}"/>
+      <Comment id="{3db4590b-99b0-46f9-8e5c-535b09fd0c09}"/>
     </Anchor>
     <History>
-      <Event time="2026-06-05T13:55:13.00" id="{6aa7667b-d93b-4be4-b33e-5689492c863a}">
+      <Event time="2026-06-05T13:55:13.00" id="{33258cc1-57c5-427e-b0cf-7728908c8532}">
         <Attribution userId="placeholder@email.com" userName="Roseneide Sena" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}"/>
+          <Comment id="{3db4590b-99b0-46f9-8e5c-535b09fd0c09}"/>
         </Anchor>
         <Create/>
       </Event>
-      <Event time="2026-06-05T13:55:13.00" id="{d38ca453-1983-4476-98ee-5aff7b39107e}">
+      <Event time="2026-06-05T13:55:13.00" id="{6e82845f-603e-460e-b6f7-d006793ace38}">
         <Attribution userId="placeholder@email.com" userName="Roseneide Sena" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}"/>
+          <Comment id="{3db4590b-99b0-46f9-8e5c-535b09fd0c09}"/>
         </Anchor>
         <Assign userId="luisalnr@gmail.com" userName="luisalnr@gmail.com" userProvider="google-sheets"/>
       </Event>
@@ -1289,11 +1283,11 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="luisalnr@gmail.com" id="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" userId="luisalnr@gmail.com" providerId="google-sheets"/>
-  <x18tc:person displayName="Roseneide Sena" id="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" providerId="google-sheets"/>
-  <x18tc:person displayName="Vinícius_Oikonomia" id="{96cb20ff-ca75-4803-bcce-b3200dd39887}" providerId="google-sheets"/>
-  <x18tc:person displayName="rsena.acre@gmail.com" id="{2b2a40fd-1d02-433a-97cf-450b5792e745}" userId="rsena.acre@gmail.com" providerId="google-sheets"/>
-  <x18tc:person displayName="Luísa Ribeiro" id="{4a970b55-9de4-44b4-b664-773b73a5c0ca}" providerId="google-sheets"/>
+  <x18tc:person displayName="luisalnr@gmail.com" id="{04d0802d-6b46-4da0-9c28-31ea27299ecf}" userId="luisalnr@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Roseneide Sena" id="{18a4e096-09dc-487e-94e2-bb4f2bc6690b}" providerId="google-sheets"/>
+  <x18tc:person displayName="Vinícius_Oikonomia" id="{4b7fa688-6db5-404c-a3ea-4ec0609ed5c5}" providerId="google-sheets"/>
+  <x18tc:person displayName="rsena.acre@gmail.com" id="{a4db4c2b-c5e8-4071-a7cd-2df124f7c271}" userId="rsena.acre@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="Luísa Ribeiro" id="{85e82f82-b122-4a5e-827e-e13eb07226b3}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1633,35 +1627,35 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E73" dT="2026-06-08T13:15:23.00" personId="{96cb20ff-ca75-4803-bcce-b3200dd39887}" id="{f06b32da-dd55-4e63-aef3-1f65e72a0c83}" done="0">
+  <x18tc:threadedComment ref="E73" dT="2026-06-08T13:15:23.00" personId="{4b7fa688-6db5-404c-a3ea-4ec0609ed5c5}" id="{bbd46d50-5793-4f27-acbb-bf2b066df97a}" done="0">
     <x18tc:text xml:space="preserve">No QDD, consta valor inicial de R$2000, consideramos R$1000 ou R$2000 @rsena.acre@gmail.com</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{2b2a40fd-1d02-433a-97cf-450b5792e745}" mentionId="{c73ce117-07e8-445d-bb33-afc23e89eae7}" startIndex="70" length="21"/>
+      <x18tc:mention mentionpersonId="{a4db4c2b-c5e8-4071-a7cd-2df124f7c271}" mentionId="{8984a4e6-8f3e-49d5-b058-f4b3f322d5a6}" startIndex="70" length="21"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E73" dT="2026-06-08T13:38:54.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{521d4cde-75cd-454b-b98e-61333b99ef39}" parentId="{f06b32da-dd55-4e63-aef3-1f65e72a0c83}">
+  <x18tc:threadedComment ref="E73" dT="2026-06-08T13:38:54.00" personId="{18a4e096-09dc-487e-94e2-bb4f2bc6690b}" id="{f4b5fff5-84a7-450b-b5b5-21ec6fe520f4}" parentId="{bbd46d50-5793-4f27-acbb-bf2b066df97a}">
     <x18tc:text xml:space="preserve">Apenas o valor relativo à obra = R$ 1.000,00</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E68" dT="2026-06-03T21:29:16.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{2a7dcfa7-c60f-45b9-842b-040baa35e254}" done="1">
+  <x18tc:threadedComment ref="E68" dT="2026-06-03T21:29:16.00" personId="{18a4e096-09dc-487e-94e2-bb4f2bc6690b}" id="{8244c2f2-4132-4074-9ca2-389a2fe912cd}" done="1">
     <x18tc:text xml:space="preserve">Verificar esse valor, pelo QDD esse Projeto/Atividade só computa R$ 47.042.981,28 @luisalnr@gmail.com</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" mentionId="{90f250da-d5e6-4196-b946-647c4ebac419}" startIndex="82" length="19"/>
+      <x18tc:mention mentionpersonId="{04d0802d-6b46-4da0-9c28-31ea27299ecf}" mentionId="{29d4e9f1-e002-40bc-a4e0-b0e90847866a}" startIndex="82" length="19"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E68" dT="2026-06-08T12:59:46.00" personId="{4a970b55-9de4-44b4-b664-773b73a5c0ca}" id="{17afef39-fefd-4e38-a3d5-af6658c0a1cb}" parentId="{2a7dcfa7-c60f-45b9-842b-040baa35e254}">
+  <x18tc:threadedComment ref="E68" dT="2026-06-08T12:59:46.00" personId="{85e82f82-b122-4a5e-827e-e13eb07226b3}" id="{e341b169-42c0-476c-bcb0-2345d3c7983a}" parentId="{8244c2f2-4132-4074-9ca2-389a2fe912cd}">
     <x18tc:text xml:space="preserve">De acordo com o SICAF, é este valor mesmo de R$ 97.285.647,31</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A73" dT="2026-06-05T13:55:13.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{c04e08d9-b3a5-458c-a077-712e51e5ccf6}" done="1">
+  <x18tc:threadedComment ref="A73" dT="2026-06-05T13:55:13.00" personId="{18a4e096-09dc-487e-94e2-bb4f2bc6690b}" id="{3db4590b-99b0-46f9-8e5c-535b09fd0c09}" done="1">
     <x18tc:text xml:space="preserve">Não apareceram os seguintes órgãos: TCE, TJAC, DPE, MPAC (estão listados na planilha anterior, mas não estão nesta) @luisalnr@gmail.com
 Assigned to luisalnr@gmail.com</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" mentionId="{d1cca60a-a306-4c14-ba9a-197043d694a9}" startIndex="116" length="19"/>
+      <x18tc:mention mentionpersonId="{04d0802d-6b46-4da0-9c28-31ea27299ecf}" mentionId="{f8e03a6e-ccfb-401d-8bf0-1a9122dca0e4}" startIndex="116" length="19"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-06-03T18:33:29.00" personId="{96b38dae-aaad-4c58-8713-07ba69f8f13c}" id="{0619dc93-171c-4da2-b441-412af1ac3113}" done="1">
+  <x18tc:threadedComment ref="A1" dT="2026-06-03T18:33:29.00" personId="{18a4e096-09dc-487e-94e2-bb4f2bc6690b}" id="{8ba3ea41-de65-44d7-bcaf-e66d12b358bb}" done="1">
     <x18tc:text xml:space="preserve">@luisalnr@gmail.com manter apenas no Eixo VI - linha 163 da planilha</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{412111f0-d9ef-41f6-b055-45c4ed45d33c}" mentionId="{942a7798-e932-4ddc-b0dd-143a787fd7f2}" startIndex="0" length="19"/>
+      <x18tc:mention mentionpersonId="{04d0802d-6b46-4da0-9c28-31ea27299ecf}" mentionId="{a71f5bba-37ab-4118-abfb-9c82b953353b}" startIndex="0" length="19"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -3523,7 +3517,7 @@
         <v>121.0</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="E74" s="28">
         <v>2.0E7</v>
@@ -3532,7 +3526,7 @@
         <v>2.228E7</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H74" s="29" t="s">
         <v>45</v>
@@ -3549,7 +3543,7 @@
         <v>122.0</v>
       </c>
       <c r="D75" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E75" s="38">
         <v>100000.0</v>
@@ -3558,7 +3552,7 @@
         <v>2.152E7</v>
       </c>
       <c r="G75" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H75" s="29" t="s">
         <v>45</v>
@@ -3575,7 +3569,7 @@
         <v>122.0</v>
       </c>
       <c r="D76" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E76" s="35">
         <f>50000+60000</f>
@@ -3585,7 +3579,7 @@
         <v>2.12E7</v>
       </c>
       <c r="G76" s="36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H76" s="29" t="s">
         <v>45</v>
@@ -3611,7 +3605,7 @@
         <v>1.197E7</v>
       </c>
       <c r="G77" s="36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H77" s="29" t="s">
         <v>45</v>
@@ -3637,13 +3631,10 @@
         <v>1.199E7</v>
       </c>
       <c r="G78" s="36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H78" s="29" t="s">
         <v>45</v>
-      </c>
-      <c r="I78" s="39">
-        <v>4.0</v>
       </c>
     </row>
     <row r="79">
@@ -3666,7 +3657,7 @@
         <v>1.203E7</v>
       </c>
       <c r="G79" s="36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H79" s="29" t="s">
         <v>45</v>
@@ -3692,7 +3683,7 @@
         <v>1.204E7</v>
       </c>
       <c r="G80" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H80" s="29" t="s">
         <v>45</v>
@@ -3718,7 +3709,7 @@
         <v>2.221E7</v>
       </c>
       <c r="G81" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H81" s="29" t="s">
         <v>45</v>
@@ -3735,7 +3726,7 @@
         <v>129.0</v>
       </c>
       <c r="D82" s="34" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="E82" s="38">
         <v>1000000.0</v>
@@ -3744,7 +3735,7 @@
         <v>1.197E7</v>
       </c>
       <c r="G82" s="36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H82" s="29" t="s">
         <v>45</v>
@@ -3761,7 +3752,7 @@
         <v>129.0</v>
       </c>
       <c r="D83" s="34" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="E83" s="38">
         <v>4000000.0</v>
@@ -3770,7 +3761,7 @@
         <v>1.203E7</v>
       </c>
       <c r="G83" s="36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H83" s="29" t="s">
         <v>45</v>
@@ -3781,7 +3772,7 @@
         <v>100</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C84" s="37">
         <v>181.0</v>
@@ -3796,7 +3787,7 @@
         <v>1.365E7</v>
       </c>
       <c r="G84" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H84" s="29" t="s">
         <v>45</v>
@@ -3807,13 +3798,13 @@
         <v>100</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C85" s="37">
         <v>182.0</v>
       </c>
       <c r="D85" s="34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E85" s="35">
         <v>1000.0</v>
@@ -3822,7 +3813,7 @@
         <v>1.015E7</v>
       </c>
       <c r="G85" s="36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H85" s="29" t="s">
         <v>45</v>
@@ -3833,13 +3824,13 @@
         <v>100</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C86" s="37">
         <v>182.0</v>
       </c>
       <c r="D86" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E86" s="38">
         <v>500000.0</v>
@@ -3848,7 +3839,7 @@
         <v>1.012E7</v>
       </c>
       <c r="G86" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H86" s="29" t="s">
         <v>45</v>
@@ -3859,13 +3850,13 @@
         <v>100</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C87" s="37">
         <v>182.0</v>
       </c>
       <c r="D87" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E87" s="38">
         <v>1999000.0</v>
@@ -3874,7 +3865,7 @@
         <v>1.014E7</v>
       </c>
       <c r="G87" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H87" s="29" t="s">
         <v>45</v>
@@ -3885,13 +3876,13 @@
         <v>100</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C88" s="33">
         <v>183.0</v>
       </c>
       <c r="D88" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E88" s="38">
         <v>200000.0</v>
@@ -3900,7 +3891,7 @@
         <v>2.075E7</v>
       </c>
       <c r="G88" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H88" s="29" t="s">
         <v>45</v>
@@ -3911,13 +3902,13 @@
         <v>100</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C89" s="37">
         <v>183.0</v>
       </c>
       <c r="D89" s="34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E89" s="35">
         <v>3300000.0</v>
@@ -3926,7 +3917,7 @@
         <v>1.105E7</v>
       </c>
       <c r="G89" s="36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H89" s="29" t="s">
         <v>45</v>
@@ -3937,13 +3928,13 @@
         <v>100</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C90" s="20">
         <v>183.0</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E90" s="28">
         <v>800.0</v>
@@ -3952,7 +3943,7 @@
         <v>1.093E7</v>
       </c>
       <c r="G90" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H90" s="29" t="s">
         <v>45</v>
@@ -3963,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C91" s="37">
         <v>183.0</v>
@@ -3971,7 +3962,7 @@
       <c r="D91" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E91" s="40">
+      <c r="E91" s="39">
         <f>600000+3700000</f>
         <v>4300000</v>
       </c>
@@ -3979,7 +3970,7 @@
         <v>1.116E7</v>
       </c>
       <c r="G91" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H91" s="29" t="s">
         <v>45</v>
@@ -3990,13 +3981,13 @@
         <v>100</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C92" s="20">
         <v>183.0</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E92" s="22">
         <v>1771713.29</v>
@@ -4005,7 +3996,7 @@
         <v>1.093E7</v>
       </c>
       <c r="G92" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H92" s="29" t="s">
         <v>45</v>
@@ -4016,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C93" s="37">
         <v>183.0</v>
@@ -4024,7 +4015,7 @@
       <c r="D93" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E93" s="40">
+      <c r="E93" s="39">
         <f>2800000</f>
         <v>2800000</v>
       </c>
@@ -4032,7 +4023,7 @@
         <v>1.116E7</v>
       </c>
       <c r="G93" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H93" s="29" t="s">
         <v>45</v>
@@ -4043,7 +4034,7 @@
         <v>100</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C94" s="37">
         <v>183.0</v>
@@ -4051,14 +4042,14 @@
       <c r="D94" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="41">
+      <c r="E94" s="40">
         <v>50000.0</v>
       </c>
       <c r="F94" s="36">
         <v>1.115E7</v>
       </c>
       <c r="G94" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H94" s="29" t="s">
         <v>45</v>
@@ -4069,7 +4060,7 @@
         <v>100</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C95" s="33">
         <v>183.0</v>
@@ -4077,14 +4068,14 @@
       <c r="D95" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E95" s="41">
+      <c r="E95" s="40">
         <v>250000.0</v>
       </c>
       <c r="F95" s="36">
         <v>1.112E7</v>
       </c>
       <c r="G95" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H95" s="29" t="s">
         <v>45</v>
@@ -4095,7 +4086,7 @@
         <v>100</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C96" s="33">
         <v>183.0</v>
@@ -4103,14 +4094,14 @@
       <c r="D96" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E96" s="41">
+      <c r="E96" s="40">
         <v>400000.0</v>
       </c>
       <c r="F96" s="36">
         <v>1.115E7</v>
       </c>
       <c r="G96" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H96" s="29" t="s">
         <v>45</v>
@@ -4121,13 +4112,13 @@
         <v>100</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C97" s="37">
         <v>183.0</v>
       </c>
       <c r="D97" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E97" s="35">
         <f>3300000</f>
@@ -4137,7 +4128,7 @@
         <v>1.022E7</v>
       </c>
       <c r="G97" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H97" s="29" t="s">
         <v>45</v>
@@ -4147,23 +4138,23 @@
       <c r="A98" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="42" t="s">
-        <v>119</v>
+      <c r="B98" s="41" t="s">
+        <v>118</v>
       </c>
       <c r="C98" s="37">
         <v>183.0</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="E98" s="41">
+        <v>132</v>
+      </c>
+      <c r="E98" s="40">
         <v>1000000.0</v>
       </c>
       <c r="F98" s="36">
         <v>2.076E7</v>
       </c>
       <c r="G98" s="36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H98" s="29" t="s">
         <v>45</v>
@@ -4174,13 +4165,13 @@
         <v>100</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C99" s="37">
         <v>421.0</v>
       </c>
       <c r="D99" s="34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E99" s="35">
         <v>1000000.0</v>
@@ -4189,7 +4180,7 @@
         <v>1.09E7</v>
       </c>
       <c r="G99" s="36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H99" s="29" t="s">
         <v>45</v>
@@ -4200,7 +4191,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C100" s="37">
         <v>542.0</v>
@@ -4226,13 +4217,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C101" s="37">
         <v>122.0</v>
       </c>
       <c r="D101" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E101" s="35">
         <v>1000.0</v>
@@ -4241,7 +4232,7 @@
         <v>2.251E7</v>
       </c>
       <c r="G101" s="36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H101" s="29" t="s">
         <v>45</v>
@@ -4252,13 +4243,13 @@
         <v>100</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C102" s="20">
         <v>244.0</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E102" s="28">
         <v>5000000.0</v>
@@ -4267,7 +4258,7 @@
         <v>1.221E7</v>
       </c>
       <c r="G102" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H102" s="29" t="s">
         <v>45</v>
@@ -4278,22 +4269,22 @@
         <v>100</v>
       </c>
       <c r="B103" s="32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C103" s="37">
         <v>122.0</v>
       </c>
       <c r="D103" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="E103" s="41">
+        <v>141</v>
+      </c>
+      <c r="E103" s="40">
         <v>100000.0</v>
       </c>
       <c r="F103" s="36">
         <v>2.019E7</v>
       </c>
       <c r="G103" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H103" s="29" t="s">
         <v>45</v>
@@ -4304,13 +4295,13 @@
         <v>100</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C104" s="20">
         <v>272.0</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E104" s="28">
         <v>4000000.0</v>
@@ -4319,7 +4310,7 @@
         <v>2.021E7</v>
       </c>
       <c r="G104" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H104" s="29" t="s">
         <v>45</v>
@@ -4330,15 +4321,15 @@
         <v>100</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C105" s="37">
         <v>302.0</v>
       </c>
       <c r="D105" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="E105" s="40">
+        <v>145</v>
+      </c>
+      <c r="E105" s="39">
         <f>44510000</f>
         <v>44510000</v>
       </c>
@@ -4346,7 +4337,7 @@
         <v>1.173E7</v>
       </c>
       <c r="G105" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H105" s="29" t="s">
         <v>45</v>
@@ -4357,13 +4348,13 @@
         <v>100</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C106" s="37">
         <v>302.0</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E106" s="38">
         <v>1.2997E7</v>
@@ -4372,7 +4363,7 @@
         <v>2.208E7</v>
       </c>
       <c r="G106" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H106" s="29" t="s">
         <v>45</v>
@@ -4383,15 +4374,15 @@
         <v>100</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C107" s="37">
         <v>695.0</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="E107" s="40">
+        <v>149</v>
+      </c>
+      <c r="E107" s="39">
         <f>700000+1</f>
         <v>700001</v>
       </c>
@@ -4399,7 +4390,7 @@
         <v>1.151E7</v>
       </c>
       <c r="G107" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H107" s="29" t="s">
         <v>45</v>
@@ -4410,13 +4401,13 @@
         <v>100</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C108" s="37">
         <v>695.0</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E108" s="38">
         <v>1.0</v>
@@ -4425,7 +4416,7 @@
         <v>1152000.0</v>
       </c>
       <c r="G108" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H108" s="29" t="s">
         <v>12</v>
@@ -4436,13 +4427,13 @@
         <v>100</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C109" s="37">
         <v>361.0</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E109" s="38">
         <v>1900000.0</v>
@@ -4451,7 +4442,7 @@
         <v>2.089E7</v>
       </c>
       <c r="G109" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H109" s="29" t="s">
         <v>45</v>
@@ -4462,13 +4453,13 @@
         <v>100</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C110" s="37">
         <v>361.0</v>
       </c>
       <c r="D110" s="34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E110" s="38">
         <v>2.495E7</v>
@@ -4477,7 +4468,7 @@
         <v>1.041E7</v>
       </c>
       <c r="G110" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H110" s="29" t="s">
         <v>45</v>
@@ -4488,13 +4479,13 @@
         <v>100</v>
       </c>
       <c r="B111" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C111" s="37">
         <v>362.0</v>
       </c>
       <c r="D111" s="34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E111" s="35">
         <f>4000000</f>
@@ -4504,7 +4495,7 @@
         <v>1.04E7</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H111" s="29" t="s">
         <v>45</v>
@@ -4515,13 +4506,13 @@
         <v>100</v>
       </c>
       <c r="B112" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C112" s="37">
         <v>363.0</v>
       </c>
       <c r="D112" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E112" s="38">
         <v>500.0</v>
@@ -4530,7 +4521,7 @@
         <v>2.082E7</v>
       </c>
       <c r="G112" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H112" s="29" t="s">
         <v>45</v>
@@ -4541,13 +4532,13 @@
         <v>100</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C113" s="37">
         <v>363.0</v>
       </c>
       <c r="D113" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E113" s="38">
         <v>500.0</v>
@@ -4556,7 +4547,7 @@
         <v>1.025E7</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H113" s="29" t="s">
         <v>45</v>
@@ -4567,13 +4558,13 @@
         <v>100</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C114" s="37">
         <v>363.0</v>
       </c>
       <c r="D114" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E114" s="38">
         <v>1601000.0</v>
@@ -4582,7 +4573,7 @@
         <v>1.023E7</v>
       </c>
       <c r="G114" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H114" s="29" t="s">
         <v>45</v>
@@ -4593,13 +4584,13 @@
         <v>100</v>
       </c>
       <c r="B115" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C115" s="37">
         <v>122.0</v>
       </c>
       <c r="D115" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E115" s="38">
         <v>147472.27</v>
@@ -4608,7 +4599,7 @@
         <v>1.299E7</v>
       </c>
       <c r="G115" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H115" s="29" t="s">
         <v>45</v>
@@ -4619,13 +4610,13 @@
         <v>100</v>
       </c>
       <c r="B116" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C116" s="37">
         <v>122.0</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E116" s="38">
         <v>151000.0</v>
@@ -4634,7 +4625,7 @@
         <v>1.299E7</v>
       </c>
       <c r="G116" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H116" s="29" t="s">
         <v>45</v>
@@ -4645,13 +4636,13 @@
         <v>100</v>
       </c>
       <c r="B117" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C117" s="33">
         <v>392.0</v>
       </c>
       <c r="D117" s="34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E117" s="38">
         <v>750000.0</v>
@@ -4660,7 +4651,7 @@
         <v>1.29E7</v>
       </c>
       <c r="G117" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H117" s="29" t="s">
         <v>45</v>
@@ -4671,13 +4662,13 @@
         <v>100</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C118" s="33">
         <v>392.0</v>
       </c>
       <c r="D118" s="34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E118" s="38">
         <v>290000.0</v>
@@ -4686,7 +4677,7 @@
         <v>1.292E7</v>
       </c>
       <c r="G118" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H118" s="29" t="s">
         <v>45</v>
@@ -4697,13 +4688,13 @@
         <v>100</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C119" s="37">
         <v>243.0</v>
       </c>
       <c r="D119" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E119" s="35">
         <v>2251384.93</v>
@@ -4712,7 +4703,7 @@
         <v>1.011E7</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H119" s="29" t="s">
         <v>45</v>
@@ -4723,13 +4714,13 @@
         <v>100</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120" s="20">
         <v>422.0</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E120" s="28">
         <v>5000.0</v>
@@ -4738,7 +4729,7 @@
         <v>1.036E7</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H120" s="29" t="s">
         <v>45</v>
@@ -4749,13 +4740,13 @@
         <v>100</v>
       </c>
       <c r="B121" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C121" s="37">
         <v>422.0</v>
       </c>
       <c r="D121" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E121" s="35">
         <v>589560.0</v>
@@ -4764,7 +4755,7 @@
         <v>1.147E7</v>
       </c>
       <c r="G121" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H121" s="29" t="s">
         <v>45</v>
@@ -4775,13 +4766,13 @@
         <v>100</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C122" s="37">
         <v>451.0</v>
       </c>
       <c r="D122" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E122" s="38">
         <v>1000.0</v>
@@ -4790,7 +4781,7 @@
         <v>1.058E7</v>
       </c>
       <c r="G122" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H122" s="29" t="s">
         <v>12</v>
@@ -4801,13 +4792,13 @@
         <v>100</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C123" s="37">
         <v>451.0</v>
       </c>
       <c r="D123" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E123" s="38">
         <v>9362139.29</v>
@@ -4816,7 +4807,7 @@
         <v>1.059E7</v>
       </c>
       <c r="G123" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H123" s="29" t="s">
         <v>12</v>
@@ -4827,13 +4818,13 @@
         <v>100</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C124" s="37">
         <v>451.0</v>
       </c>
       <c r="D124" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E124" s="38">
         <v>3.49143533E7</v>
@@ -4842,7 +4833,7 @@
         <v>1.06E7</v>
       </c>
       <c r="G124" s="36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H124" s="29" t="s">
         <v>45</v>
@@ -4853,13 +4844,13 @@
         <v>100</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C125" s="37">
         <v>451.0</v>
       </c>
       <c r="D125" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E125" s="38">
         <v>1001000.0</v>
@@ -4868,7 +4859,7 @@
         <v>1.061E7</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H125" s="29" t="s">
         <v>45</v>
@@ -4879,13 +4870,13 @@
         <v>100</v>
       </c>
       <c r="B126" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C126" s="37">
         <v>451.0</v>
       </c>
       <c r="D126" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E126" s="38">
         <v>1000.0</v>
@@ -4894,7 +4885,7 @@
         <v>1.34E7</v>
       </c>
       <c r="G126" s="36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H126" s="29" t="s">
         <v>45</v>
@@ -4905,13 +4896,13 @@
         <v>100</v>
       </c>
       <c r="B127" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C127" s="37">
         <v>451.0</v>
       </c>
       <c r="D127" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E127" s="38">
         <v>1000.0</v>
@@ -4920,7 +4911,7 @@
         <v>2.306E7</v>
       </c>
       <c r="G127" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H127" s="29" t="s">
         <v>45</v>
@@ -4931,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="B128" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C128" s="37">
         <v>451.0</v>
@@ -4946,7 +4937,7 @@
         <v>1.099E7</v>
       </c>
       <c r="G128" s="36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H128" s="29" t="s">
         <v>12</v>
@@ -4957,7 +4948,7 @@
         <v>100</v>
       </c>
       <c r="B129" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C129" s="37">
         <v>451.0</v>
@@ -4972,7 +4963,7 @@
         <v>2.201E7</v>
       </c>
       <c r="G129" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H129" s="29" t="s">
         <v>45</v>
@@ -4983,13 +4974,13 @@
         <v>100</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C130" s="20">
         <v>451.0</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E130" s="28">
         <v>1000.0</v>
@@ -4998,7 +4989,7 @@
         <v>1.059E7</v>
       </c>
       <c r="G130" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H130" s="29" t="s">
         <v>12</v>
@@ -5009,13 +5000,13 @@
         <v>100</v>
       </c>
       <c r="B131" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C131" s="37">
         <v>451.0</v>
       </c>
       <c r="D131" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E131" s="38">
         <v>1.78625E7</v>
@@ -5024,7 +5015,7 @@
         <v>1.097E7</v>
       </c>
       <c r="G131" s="36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H131" s="29" t="s">
         <v>45</v>
@@ -5035,13 +5026,13 @@
         <v>100</v>
       </c>
       <c r="B132" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C132" s="37">
         <v>451.0</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E132" s="38">
         <v>9938000.0</v>
@@ -5050,7 +5041,7 @@
         <v>1.098E7</v>
       </c>
       <c r="G132" s="36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H132" s="29" t="s">
         <v>45</v>
@@ -5061,13 +5052,13 @@
         <v>100</v>
       </c>
       <c r="B133" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C133" s="37">
         <v>451.0</v>
       </c>
       <c r="D133" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E133" s="38">
         <f>4800000+3600000+9000000</f>
@@ -5077,7 +5068,7 @@
         <v>1.099E7</v>
       </c>
       <c r="G133" s="36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H133" s="29" t="s">
         <v>12</v>
@@ -5088,13 +5079,13 @@
         <v>100</v>
       </c>
       <c r="B134" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C134" s="37">
         <v>451.0</v>
       </c>
       <c r="D134" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E134" s="38">
         <v>5705000.0</v>
@@ -5103,7 +5094,7 @@
         <v>1.1E7</v>
       </c>
       <c r="G134" s="36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H134" s="29" t="s">
         <v>45</v>
@@ -5114,13 +5105,13 @@
         <v>100</v>
       </c>
       <c r="B135" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C135" s="37">
         <v>451.0</v>
       </c>
       <c r="D135" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E135" s="38">
         <v>1.0E7</v>
@@ -5129,7 +5120,7 @@
         <v>1.331E7</v>
       </c>
       <c r="G135" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H135" s="29" t="s">
         <v>45</v>
@@ -5140,13 +5131,13 @@
         <v>100</v>
       </c>
       <c r="B136" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C136" s="37">
         <v>451.0</v>
       </c>
       <c r="D136" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E136" s="38">
         <v>1.6034E7</v>
@@ -5155,7 +5146,7 @@
         <v>2.142E7</v>
       </c>
       <c r="G136" s="36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H136" s="29" t="s">
         <v>45</v>
@@ -5166,15 +5157,15 @@
         <v>100</v>
       </c>
       <c r="B137" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C137" s="37">
         <v>512.0</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="E137" s="40">
+        <v>175</v>
+      </c>
+      <c r="E137" s="39">
         <f>3000</f>
         <v>3000</v>
       </c>
@@ -5182,7 +5173,7 @@
         <v>1.337E7</v>
       </c>
       <c r="G137" s="36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H137" s="29" t="s">
         <v>45</v>
@@ -5193,13 +5184,13 @@
         <v>100</v>
       </c>
       <c r="B138" s="32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C138" s="37">
         <v>122.0</v>
       </c>
       <c r="D138" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E138" s="38">
         <v>150000.0</v>
@@ -5208,7 +5199,7 @@
         <v>2.275E7</v>
       </c>
       <c r="G138" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H138" s="29" t="s">
         <v>45</v>
@@ -5219,13 +5210,13 @@
         <v>100</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C139" s="20">
         <v>482.0</v>
       </c>
       <c r="D139" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E139" s="28">
         <v>100000.0</v>
@@ -5234,7 +5225,7 @@
         <v>1.057E7</v>
       </c>
       <c r="G139" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H139" s="29" t="s">
         <v>45</v>
@@ -5245,22 +5236,22 @@
         <v>100</v>
       </c>
       <c r="B140" s="32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C140" s="37">
         <v>482.0</v>
       </c>
       <c r="D140" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="E140" s="41">
+        <v>175</v>
+      </c>
+      <c r="E140" s="40">
         <v>7541842.2</v>
       </c>
       <c r="F140" s="36">
         <v>1.057E7</v>
       </c>
       <c r="G140" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H140" s="29" t="s">
         <v>45</v>
@@ -5271,13 +5262,13 @@
         <v>100</v>
       </c>
       <c r="B141" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C141" s="37">
         <v>512.0</v>
       </c>
       <c r="D141" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E141" s="38">
         <v>3000.0</v>
@@ -5286,7 +5277,7 @@
         <v>1.338E7</v>
       </c>
       <c r="G141" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H141" s="29" t="s">
         <v>45</v>
@@ -5297,13 +5288,13 @@
         <v>100</v>
       </c>
       <c r="B142" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C142" s="20">
         <v>512.0</v>
       </c>
       <c r="D142" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E142" s="22">
         <v>3221000.0</v>
@@ -5312,7 +5303,7 @@
         <v>1.101E7</v>
       </c>
       <c r="G142" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H142" s="29" t="s">
         <v>45</v>
@@ -5323,13 +5314,13 @@
         <v>100</v>
       </c>
       <c r="B143" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C143" s="20">
         <v>512.0</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E143" s="22">
         <v>1000000.0</v>
@@ -5338,7 +5329,7 @@
         <v>1.102E7</v>
       </c>
       <c r="G143" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H143" s="29" t="s">
         <v>45</v>
@@ -5349,13 +5340,13 @@
         <v>100</v>
       </c>
       <c r="B144" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C144" s="20">
         <v>512.0</v>
       </c>
       <c r="D144" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E144" s="22">
         <v>8550000.0</v>
@@ -5364,7 +5355,7 @@
         <v>1.103E7</v>
       </c>
       <c r="G144" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H144" s="29" t="s">
         <v>45</v>
@@ -5375,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="B145" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C145" s="37">
         <v>512.0</v>
@@ -5390,7 +5381,7 @@
         <v>1.129E7</v>
       </c>
       <c r="G145" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H145" s="29" t="s">
         <v>45</v>
@@ -5401,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="B146" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C146" s="37">
         <v>512.0</v>
@@ -5416,7 +5407,7 @@
         <v>1130000.0</v>
       </c>
       <c r="G146" s="36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H146" s="29" t="s">
         <v>45</v>
@@ -5427,7 +5418,7 @@
         <v>100</v>
       </c>
       <c r="B147" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C147" s="20">
         <v>512.0</v>
@@ -5442,7 +5433,7 @@
         <v>1.045E7</v>
       </c>
       <c r="G147" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H147" s="29" t="s">
         <v>45</v>
@@ -5494,7 +5485,7 @@
         <v>1.138E7</v>
       </c>
       <c r="G149" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H149" s="29" t="s">
         <v>45</v>
@@ -5505,13 +5496,13 @@
         <v>100</v>
       </c>
       <c r="B150" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C150" s="37">
         <v>571.0</v>
       </c>
       <c r="D150" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E150" s="35">
         <v>10.0</v>
@@ -5520,7 +5511,7 @@
         <v>1.156E7</v>
       </c>
       <c r="G150" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H150" s="29" t="s">
         <v>45</v>
@@ -5546,7 +5537,7 @@
         <v>1.084E7</v>
       </c>
       <c r="G151" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H151" s="29" t="s">
         <v>45</v>
@@ -5563,7 +5554,7 @@
         <v>451.0</v>
       </c>
       <c r="D152" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E152" s="35">
         <v>2000000.0</v>
@@ -5572,7 +5563,7 @@
         <v>1.073E7</v>
       </c>
       <c r="G152" s="36" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H152" s="29" t="s">
         <v>45</v>
@@ -5636,13 +5627,13 @@
         <v>100</v>
       </c>
       <c r="B155" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C155" s="37">
         <v>127.0</v>
       </c>
       <c r="D155" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E155" s="38">
         <v>1000.0</v>
@@ -5651,7 +5642,7 @@
         <v>1.339E7</v>
       </c>
       <c r="G155" s="36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H155" s="29" t="s">
         <v>45</v>
@@ -5662,7 +5653,7 @@
         <v>100</v>
       </c>
       <c r="B156" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C156" s="37">
         <v>122.0</v>
@@ -5677,7 +5668,7 @@
         <v>2.203E7</v>
       </c>
       <c r="G156" s="36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H156" s="29" t="s">
         <v>45</v>
@@ -5688,7 +5679,7 @@
         <v>100</v>
       </c>
       <c r="B157" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C157" s="37">
         <v>451.0</v>
@@ -5703,7 +5694,7 @@
         <v>1.171E7</v>
       </c>
       <c r="G157" s="36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H157" s="29" t="s">
         <v>45</v>
@@ -5714,7 +5705,7 @@
         <v>100</v>
       </c>
       <c r="B158" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C158" s="37">
         <v>781.0</v>
@@ -5729,7 +5720,7 @@
         <v>1.168E7</v>
       </c>
       <c r="G158" s="36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H158" s="29" t="s">
         <v>45</v>
@@ -5740,7 +5731,7 @@
         <v>100</v>
       </c>
       <c r="B159" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C159" s="37">
         <v>782.0</v>
@@ -5755,7 +5746,7 @@
         <v>1.169E7</v>
       </c>
       <c r="G159" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H159" s="29" t="s">
         <v>45</v>
@@ -5766,7 +5757,7 @@
         <v>100</v>
       </c>
       <c r="B160" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C160" s="37">
         <v>782.0</v>
@@ -5781,7 +5772,7 @@
         <v>2.196E7</v>
       </c>
       <c r="G160" s="36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H160" s="29" t="s">
         <v>45</v>
@@ -5792,7 +5783,7 @@
         <v>100</v>
       </c>
       <c r="B161" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C161" s="37">
         <v>782.0</v>
@@ -5807,7 +5798,7 @@
         <v>2.197E7</v>
       </c>
       <c r="G161" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H161" s="29" t="s">
         <v>45</v>
@@ -5818,7 +5809,7 @@
         <v>100</v>
       </c>
       <c r="B162" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C162" s="37">
         <v>782.0</v>
@@ -5833,7 +5824,7 @@
         <v>2.198E7</v>
       </c>
       <c r="G162" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H162" s="29" t="s">
         <v>45</v>
@@ -5844,7 +5835,7 @@
         <v>100</v>
       </c>
       <c r="B163" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C163" s="37">
         <v>782.0</v>
@@ -5859,7 +5850,7 @@
         <v>2.199E7</v>
       </c>
       <c r="G163" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H163" s="29" t="s">
         <v>45</v>
@@ -5870,7 +5861,7 @@
         <v>100</v>
       </c>
       <c r="B164" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C164" s="37">
         <v>782.0</v>
@@ -5885,7 +5876,7 @@
         <v>2.2E7</v>
       </c>
       <c r="G164" s="36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H164" s="29" t="s">
         <v>45</v>
@@ -5896,13 +5887,13 @@
         <v>100</v>
       </c>
       <c r="B165" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C165" s="37">
         <v>812.0</v>
       </c>
       <c r="D165" s="34" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E165" s="35">
         <v>4466051.73</v>
@@ -5911,14 +5902,14 @@
         <v>1.332E7</v>
       </c>
       <c r="G165" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H165" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="166">
-      <c r="F166" s="43"/>
+      <c r="F166" s="42"/>
       <c r="G166" s="18"/>
       <c r="H166" s="18"/>
     </row>
@@ -5948,16 +5939,16 @@
     </row>
     <row r="168">
       <c r="A168" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B168" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B168" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C168" s="20">
         <v>244.0</v>
       </c>
       <c r="D168" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E168" s="22">
         <v>79000.0</v>
@@ -5966,7 +5957,7 @@
         <v>1.222E7</v>
       </c>
       <c r="G168" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H168" s="25" t="s">
         <v>45</v>
@@ -5974,16 +5965,16 @@
     </row>
     <row r="169">
       <c r="A169" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B169" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B169" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C169" s="20">
         <v>244.0</v>
       </c>
       <c r="D169" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E169" s="22">
         <v>1000000.0</v>
@@ -5992,7 +5983,7 @@
         <v>1.236E7</v>
       </c>
       <c r="G169" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H169" s="25" t="s">
         <v>45</v>
@@ -6000,16 +5991,16 @@
     </row>
     <row r="170">
       <c r="A170" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B170" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B170" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C170" s="20">
         <v>244.0</v>
       </c>
       <c r="D170" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E170" s="22">
         <v>69000.0</v>
@@ -6018,7 +6009,7 @@
         <v>1.254E7</v>
       </c>
       <c r="G170" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H170" s="25" t="s">
         <v>45</v>
@@ -6026,16 +6017,16 @@
     </row>
     <row r="171">
       <c r="A171" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B171" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B171" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C171" s="20">
         <v>244.0</v>
       </c>
       <c r="D171" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E171" s="22">
         <v>800000.0</v>
@@ -6044,7 +6035,7 @@
         <v>1.266E7</v>
       </c>
       <c r="G171" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H171" s="25" t="s">
         <v>12</v>
@@ -6052,16 +6043,16 @@
     </row>
     <row r="172">
       <c r="A172" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B172" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B172" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C172" s="20">
         <v>244.0</v>
       </c>
       <c r="D172" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E172" s="22">
         <v>529000.0</v>
@@ -6070,7 +6061,7 @@
         <v>1.249E7</v>
       </c>
       <c r="G172" s="23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H172" s="29" t="s">
         <v>12</v>
@@ -6078,16 +6069,16 @@
     </row>
     <row r="173">
       <c r="A173" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B173" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B173" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C173" s="20">
         <v>244.0</v>
       </c>
       <c r="D173" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E173" s="22">
         <v>50000.0</v>
@@ -6096,7 +6087,7 @@
         <v>1.266E7</v>
       </c>
       <c r="G173" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H173" s="29" t="s">
         <v>12</v>
@@ -6104,16 +6095,16 @@
     </row>
     <row r="174">
       <c r="A174" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B174" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C174" s="20">
         <v>422.0</v>
       </c>
       <c r="D174" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E174" s="28">
         <v>65200.0</v>
@@ -6122,7 +6113,7 @@
         <v>1.043E7</v>
       </c>
       <c r="G174" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H174" s="25" t="s">
         <v>45</v>
@@ -6130,16 +6121,16 @@
     </row>
     <row r="175">
       <c r="A175" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B175" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C175" s="20">
         <v>422.0</v>
       </c>
       <c r="D175" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E175" s="28">
         <v>580000.0</v>
@@ -6148,7 +6139,7 @@
         <v>1.223E7</v>
       </c>
       <c r="G175" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H175" s="25" t="s">
         <v>45</v>
@@ -6156,16 +6147,16 @@
     </row>
     <row r="176">
       <c r="A176" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B176" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C176" s="20">
         <v>422.0</v>
       </c>
       <c r="D176" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E176" s="22">
         <v>178000.0</v>
@@ -6174,7 +6165,7 @@
         <v>1.027E7</v>
       </c>
       <c r="G176" s="23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H176" s="25" t="s">
         <v>45</v>
@@ -6182,16 +6173,16 @@
     </row>
     <row r="177">
       <c r="A177" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B177" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C177" s="20">
         <v>422.0</v>
       </c>
       <c r="D177" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E177" s="22">
         <v>71000.0</v>
@@ -6200,7 +6191,7 @@
         <v>1.028E7</v>
       </c>
       <c r="G177" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H177" s="25" t="s">
         <v>45</v>
@@ -6208,16 +6199,16 @@
     </row>
     <row r="178">
       <c r="A178" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B178" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C178" s="20">
         <v>422.0</v>
       </c>
       <c r="D178" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E178" s="22">
         <v>321000.0</v>
@@ -6226,7 +6217,7 @@
         <v>1.029E7</v>
       </c>
       <c r="G178" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H178" s="25" t="s">
         <v>45</v>
@@ -6234,16 +6225,16 @@
     </row>
     <row r="179">
       <c r="A179" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C179" s="20">
         <v>422.0</v>
       </c>
       <c r="D179" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E179" s="22">
         <v>221000.0</v>
@@ -6252,7 +6243,7 @@
         <v>1.03E7</v>
       </c>
       <c r="G179" s="23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H179" s="25" t="s">
         <v>45</v>
@@ -6260,16 +6251,16 @@
     </row>
     <row r="180">
       <c r="A180" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B180" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C180" s="20">
         <v>422.0</v>
       </c>
       <c r="D180" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E180" s="22">
         <v>4048000.0</v>
@@ -6278,7 +6269,7 @@
         <v>2.083E7</v>
       </c>
       <c r="G180" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H180" s="25" t="s">
         <v>45</v>
@@ -6286,16 +6277,16 @@
     </row>
     <row r="181">
       <c r="A181" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B181" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C181" s="20">
         <v>422.0</v>
       </c>
       <c r="D181" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E181" s="28">
         <v>1030000.0</v>
@@ -6304,7 +6295,7 @@
         <v>1.035E7</v>
       </c>
       <c r="G181" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H181" s="25" t="s">
         <v>45</v>
@@ -6312,16 +6303,16 @@
     </row>
     <row r="182">
       <c r="A182" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B182" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C182" s="20">
         <v>422.0</v>
       </c>
       <c r="D182" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E182" s="28">
         <f>2415560-1937560</f>
@@ -6331,7 +6322,7 @@
         <v>1.146E7</v>
       </c>
       <c r="G182" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H182" s="25" t="s">
         <v>45</v>
@@ -6339,16 +6330,16 @@
     </row>
     <row r="183">
       <c r="A183" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B183" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C183" s="20">
         <v>423.0</v>
       </c>
       <c r="D183" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E183" s="22">
         <v>2000.0</v>
@@ -6357,7 +6348,7 @@
         <v>1.086E7</v>
       </c>
       <c r="G183" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H183" s="29" t="s">
         <v>12</v>
@@ -6365,16 +6356,16 @@
     </row>
     <row r="184">
       <c r="A184" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B184" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C184" s="20">
         <v>423.0</v>
       </c>
       <c r="D184" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E184" s="22">
         <v>2000.0</v>
@@ -6383,7 +6374,7 @@
         <v>1.087E7</v>
       </c>
       <c r="G184" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H184" s="29" t="s">
         <v>12</v>
@@ -6391,16 +6382,16 @@
     </row>
     <row r="185">
       <c r="A185" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B185" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C185" s="20">
         <v>127.0</v>
       </c>
       <c r="D185" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E185" s="28">
         <v>1151000.0</v>
@@ -6409,7 +6400,7 @@
         <v>1.339E7</v>
       </c>
       <c r="G185" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H185" s="25" t="s">
         <v>45</v>
@@ -6417,16 +6408,16 @@
     </row>
     <row r="186">
       <c r="A186" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C186" s="20">
         <v>127.0</v>
       </c>
       <c r="D186" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E186" s="22">
         <v>797700.0</v>
@@ -6435,7 +6426,7 @@
         <v>1.031E7</v>
       </c>
       <c r="G186" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H186" s="25" t="s">
         <v>45</v>
@@ -6443,16 +6434,16 @@
     </row>
     <row r="187">
       <c r="A187" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B187" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C187" s="20">
         <v>127.0</v>
       </c>
       <c r="D187" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E187" s="22">
         <v>5156900.0</v>
@@ -6461,7 +6452,7 @@
         <v>1.032E7</v>
       </c>
       <c r="G187" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H187" s="25" t="s">
         <v>45</v>
@@ -6469,16 +6460,16 @@
     </row>
     <row r="188">
       <c r="A188" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B188" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C188" s="20">
         <v>127.0</v>
       </c>
       <c r="D188" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E188" s="22">
         <v>102000.0</v>
@@ -6487,7 +6478,7 @@
         <v>1.033E7</v>
       </c>
       <c r="G188" s="23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H188" s="25" t="s">
         <v>45</v>
@@ -6495,16 +6486,16 @@
     </row>
     <row r="189">
       <c r="A189" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B189" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C189" s="20">
         <v>127.0</v>
       </c>
       <c r="D189" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E189" s="22">
         <v>20000.0</v>
@@ -6513,7 +6504,7 @@
         <v>1.034E7</v>
       </c>
       <c r="G189" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H189" s="25" t="s">
         <v>45</v>
@@ -6521,16 +6512,16 @@
     </row>
     <row r="190">
       <c r="A190" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B190" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C190" s="20">
         <v>127.0</v>
       </c>
       <c r="D190" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E190" s="22">
         <v>6110535.52</v>
@@ -6539,7 +6530,7 @@
         <v>2.084E7</v>
       </c>
       <c r="G190" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H190" s="25" t="s">
         <v>45</v>
@@ -6578,16 +6569,16 @@
     </row>
     <row r="193">
       <c r="A193" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B193" s="19" t="s">
         <v>252</v>
-      </c>
-      <c r="B193" s="19" t="s">
-        <v>253</v>
       </c>
       <c r="C193" s="20">
         <v>124.0</v>
       </c>
       <c r="D193" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E193" s="28">
         <v>660000.0</v>
@@ -6596,15 +6587,15 @@
         <v>1.085E7</v>
       </c>
       <c r="G193" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="H193" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="H193" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B194" s="19" t="s">
         <v>9</v>
@@ -6621,16 +6612,16 @@
       <c r="F194" s="23">
         <v>1.126E7</v>
       </c>
-      <c r="G194" s="45" t="s">
+      <c r="G194" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="H194" s="44" t="s">
+      <c r="H194" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B195" s="19" t="s">
         <v>9</v>
@@ -6647,10 +6638,10 @@
       <c r="F195" s="23">
         <v>1.141E7</v>
       </c>
-      <c r="G195" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="H195" s="44" t="s">
+      <c r="G195" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="H195" s="43" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6687,7 +6678,7 @@
     </row>
     <row r="198">
       <c r="A198" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B198" s="19" t="s">
         <v>73</v>
@@ -6713,7 +6704,7 @@
     </row>
     <row r="199">
       <c r="A199" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B199" s="19" t="s">
         <v>73</v>
@@ -6739,16 +6730,16 @@
     </row>
     <row r="200">
       <c r="A200" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B200" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="B200" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="C200" s="20">
         <v>571.0</v>
       </c>
       <c r="D200" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E200" s="28">
         <v>60.0</v>
@@ -6757,7 +6748,7 @@
         <v>1.156E7</v>
       </c>
       <c r="G200" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H200" s="25" t="s">
         <v>12</v>
@@ -6765,16 +6756,16 @@
     </row>
     <row r="201">
       <c r="A201" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B201" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="B201" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="C201" s="20">
         <v>573.0</v>
       </c>
       <c r="D201" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E201" s="22">
         <v>1156486.0</v>
@@ -6783,7 +6774,7 @@
         <v>1.219E7</v>
       </c>
       <c r="G201" s="23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H201" s="25" t="s">
         <v>12</v>
@@ -6791,16 +6782,16 @@
     </row>
     <row r="202">
       <c r="A202" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B202" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="B202" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="C202" s="20">
         <v>573.0</v>
       </c>
       <c r="D202" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E202" s="22">
         <v>1.0</v>
@@ -6809,7 +6800,7 @@
         <v>1.22E7</v>
       </c>
       <c r="G202" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H202" s="25" t="s">
         <v>12</v>
@@ -6817,16 +6808,16 @@
     </row>
     <row r="203">
       <c r="A203" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B203" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="B203" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="C203" s="20">
         <v>573.0</v>
       </c>
       <c r="D203" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E203" s="22">
         <v>1.0</v>
@@ -6835,7 +6826,7 @@
         <v>1.278E7</v>
       </c>
       <c r="G203" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H203" s="25" t="s">
         <v>12</v>
@@ -6843,16 +6834,16 @@
     </row>
     <row r="204">
       <c r="A204" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B204" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="B204" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="C204" s="20">
         <v>573.0</v>
       </c>
       <c r="D204" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E204" s="22">
         <v>2.0</v>
@@ -6861,7 +6852,7 @@
         <v>1.28E7</v>
       </c>
       <c r="G204" s="23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H204" s="25" t="s">
         <v>12</v>
@@ -6869,10 +6860,10 @@
     </row>
     <row r="205">
       <c r="A205" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B205" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C205" s="20">
         <v>573.0</v>
@@ -6887,7 +6878,7 @@
         <v>1.341E7</v>
       </c>
       <c r="G205" s="23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H205" s="25" t="s">
         <v>12</v>
@@ -6895,10 +6886,10 @@
     </row>
     <row r="206">
       <c r="A206" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B206" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C206" s="20">
         <v>573.0</v>
@@ -6913,7 +6904,7 @@
         <v>1.342E7</v>
       </c>
       <c r="G206" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H206" s="25" t="s">
         <v>12</v>
@@ -6921,10 +6912,10 @@
     </row>
     <row r="207">
       <c r="A207" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B207" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C207" s="20">
         <v>573.0</v>
@@ -6939,7 +6930,7 @@
         <v>1.343E7</v>
       </c>
       <c r="G207" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H207" s="25" t="s">
         <v>12</v>
@@ -6947,16 +6938,16 @@
     </row>
     <row r="208">
       <c r="A208" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B208" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C208" s="20">
         <v>573.0</v>
       </c>
       <c r="D208" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E208" s="28">
         <v>700050.0</v>
@@ -6965,7 +6956,7 @@
         <v>1.158E7</v>
       </c>
       <c r="G208" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H208" s="25" t="s">
         <v>12</v>
@@ -7004,16 +6995,16 @@
     </row>
     <row r="211">
       <c r="A211" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B211" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C211" s="20">
         <v>182.0</v>
       </c>
       <c r="D211" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E211" s="22">
         <v>4000.0</v>
@@ -7021,8 +7012,8 @@
       <c r="F211" s="23">
         <v>1.013E7</v>
       </c>
-      <c r="G211" s="46" t="s">
-        <v>270</v>
+      <c r="G211" s="45" t="s">
+        <v>269</v>
       </c>
       <c r="H211" s="25" t="s">
         <v>12</v>
@@ -7030,16 +7021,16 @@
     </row>
     <row r="212">
       <c r="A212" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B212" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C212" s="20">
         <v>182.0</v>
       </c>
       <c r="D212" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E212" s="22">
         <v>589667.0</v>
@@ -7047,8 +7038,8 @@
       <c r="F212" s="23">
         <v>2.272E7</v>
       </c>
-      <c r="G212" s="46" t="s">
-        <v>271</v>
+      <c r="G212" s="45" t="s">
+        <v>270</v>
       </c>
       <c r="H212" s="25" t="s">
         <v>12</v>
@@ -7056,16 +7047,16 @@
     </row>
     <row r="213">
       <c r="A213" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B213" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C213" s="20">
         <v>182.0</v>
       </c>
       <c r="D213" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E213" s="28">
         <v>1.7753E7</v>
@@ -7073,8 +7064,8 @@
       <c r="F213" s="23">
         <v>2.079E7</v>
       </c>
-      <c r="G213" s="46" t="s">
-        <v>272</v>
+      <c r="G213" s="45" t="s">
+        <v>271</v>
       </c>
       <c r="H213" s="25" t="s">
         <v>12</v>
@@ -7082,16 +7073,16 @@
     </row>
     <row r="214">
       <c r="A214" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B214" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="B214" s="19" t="s">
-        <v>227</v>
       </c>
       <c r="C214" s="20">
         <v>244.0</v>
       </c>
       <c r="D214" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E214" s="28">
         <v>250000.0</v>
@@ -7099,15 +7090,15 @@
       <c r="F214" s="23">
         <v>1.242E7</v>
       </c>
-      <c r="G214" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="H214" s="47" t="s">
+      <c r="G214" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="H214" s="46" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="215">
-      <c r="F215" s="48"/>
+      <c r="F215" s="47"/>
     </row>
   </sheetData>
   <dataValidations>
